--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_5oct26_Mon.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_5oct26_Mon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2E98F7-B202-4862-871B-2E0C6B71AEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F6ACE6-B348-49F8-B145-2A059727FCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3525" uniqueCount="321">
   <si>
     <t>Date</t>
   </si>
@@ -1160,7 +1160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1329,17 +1329,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="22" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1747,7 +1750,7 @@
         <v>10880</v>
       </c>
       <c r="N2" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B2, $C$2:$C$689, C2, $D$2:$D$689, D2, $E$2:$E$689, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$689, B2, $C$2:$C$689, C2, $D$2:$D$689, D2, $E$2:$E$689, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -1788,7 +1791,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B3, $C$2:$C$689, C3, $D$2:$D$689, D3, $E$2:$E$689, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1834,7 +1837,7 @@
         <v>10680</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B4, $C$2:$C$689, C4, $D$2:$D$689, D4, $E$2:$E$689, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -1875,7 +1878,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B5, $C$2:$C$689, C5, $D$2:$D$689, D5, $E$2:$E$689, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1914,7 +1917,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B6, $C$2:$C$689, C6, $D$2:$D$689, D6, $E$2:$E$689, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1951,7 +1954,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B7, $C$2:$C$689, C7, $D$2:$D$689, D7, $E$2:$E$689, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1988,7 +1991,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B8, $C$2:$C$689, C8, $D$2:$D$689, D8, $E$2:$E$689, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2027,7 +2030,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B9, $C$2:$C$689, C9, $D$2:$D$689, D9, $E$2:$E$689, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2066,7 +2069,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B10, $C$2:$C$689, C10, $D$2:$D$689, D10, $E$2:$E$689, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2103,7 +2106,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B11, $C$2:$C$689, C11, $D$2:$D$689, D11, $E$2:$E$689, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2142,7 +2145,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B12, $C$2:$C$689, C12, $D$2:$D$689, D12, $E$2:$E$689, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2179,7 +2182,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B13, $C$2:$C$689, C13, $D$2:$D$689, D13, $E$2:$E$689, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2219,7 +2222,7 @@
         <v>3156</v>
       </c>
       <c r="N14" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B14, $C$2:$C$689, C14, $D$2:$D$689, D14, $E$2:$E$689, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P14" s="19"/>
@@ -2266,7 +2269,7 @@
         <v>240</v>
       </c>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B15, $C$2:$C$689, C15, $D$2:$D$689, D15, $E$2:$E$689, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2303,7 +2306,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B16, $C$2:$C$689, C16, $D$2:$D$689, D16, $E$2:$E$689, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16"/>
@@ -2342,7 +2345,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B17, $C$2:$C$689, C17, $D$2:$D$689, D17, $E$2:$E$689, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17"/>
@@ -2383,7 +2386,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B18, $C$2:$C$689, C18, $D$2:$D$689, D18, $E$2:$E$689, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18"/>
@@ -2422,7 +2425,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B19, $C$2:$C$689, C19, $D$2:$D$689, D19, $E$2:$E$689, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -2470,7 +2473,7 @@
         <v>295</v>
       </c>
       <c r="N20" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B20, $C$2:$C$689, C20, $D$2:$D$689, D20, $E$2:$E$689, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="10"/>
@@ -2509,7 +2512,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B21, $C$2:$C$689, C21, $D$2:$D$689, D21, $E$2:$E$689, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21"/>
@@ -2557,7 +2560,7 @@
         <v>253</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B22, $C$2:$C$689, C22, $D$2:$D$689, D22, $E$2:$E$689, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2596,7 +2599,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B23, $C$2:$C$689, C23, $D$2:$D$689, D23, $E$2:$E$689, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -2635,7 +2638,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B24, $C$2:$C$689, C24, $D$2:$D$689, D24, $E$2:$E$689, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -2674,7 +2677,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B25, $C$2:$C$689, C25, $D$2:$D$689, D25, $E$2:$E$689, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
@@ -2713,7 +2716,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B26, $C$2:$C$689, C26, $D$2:$D$689, D26, $E$2:$E$689, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -2752,7 +2755,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B27, $C$2:$C$689, C27, $D$2:$D$689, D27, $E$2:$E$689, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -2801,10 +2804,9 @@
         <v>650</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B28, $C$2:$C$689, C28, $D$2:$D$689, D28, $E$2:$E$689, E28) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O28" s="58"/>
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
@@ -2843,7 +2845,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B29, $C$2:$C$689, C29, $D$2:$D$689, D29, $E$2:$E$689, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -2884,7 +2886,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B30, $C$2:$C$689, C30, $D$2:$D$689, D30, $E$2:$E$689, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P30"/>
@@ -2922,7 +2924,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B31, $C$2:$C$689, C31, $D$2:$D$689, D31, $E$2:$E$689, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -2963,7 +2965,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B32, $C$2:$C$689, C32, $D$2:$D$689, D32, $E$2:$E$689, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P32" s="25"/>
@@ -3011,7 +3013,7 @@
         <v>225</v>
       </c>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B33, $C$2:$C$689, C33, $D$2:$D$689, D33, $E$2:$E$689, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3050,7 +3052,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B34, $C$2:$C$689, C34, $D$2:$D$689, D34, $E$2:$E$689, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -3099,7 +3101,7 @@
         <v>540</v>
       </c>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B35, $C$2:$C$689, C35, $D$2:$D$689, D35, $E$2:$E$689, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -3138,7 +3140,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B36, $C$2:$C$689, C36, $D$2:$D$689, D36, $E$2:$E$689, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -3177,7 +3179,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B37, $C$2:$C$689, C37, $D$2:$D$689, D37, $E$2:$E$689, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -3224,7 +3226,7 @@
         <v>300</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B38, $C$2:$C$689, C38, $D$2:$D$689, D38, $E$2:$E$689, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -3265,7 +3267,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B39, $C$2:$C$689, C39, $D$2:$D$689, D39, $E$2:$E$689, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -3313,7 +3315,7 @@
         <v>300</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B40, $C$2:$C$689, C40, $D$2:$D$689, D40, $E$2:$E$689, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P40" s="24"/>
@@ -3360,7 +3362,7 @@
         <v>516</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B41, $C$2:$C$689, C41, $D$2:$D$689, D41, $E$2:$E$689, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3399,7 +3401,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B42, $C$2:$C$689, C42, $D$2:$D$689, D42, $E$2:$E$689, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -3440,7 +3442,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B43, $C$2:$C$689, C43, $D$2:$D$689, D43, $E$2:$E$689, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -3481,7 +3483,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B44, $C$2:$C$689, C44, $D$2:$D$689, D44, $E$2:$E$689, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3522,7 +3524,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B45, $C$2:$C$689, C45, $D$2:$D$689, D45, $E$2:$E$689, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3561,7 +3563,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B46, $C$2:$C$689, C46, $D$2:$D$689, D46, $E$2:$E$689, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="10"/>
@@ -3595,14 +3597,14 @@
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="60" t="s">
+      <c r="J47" s="57" t="s">
         <v>40</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B47, $C$2:$C$689, C47, $D$2:$D$689, D47, $E$2:$E$689, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47" s="10"/>
@@ -3636,14 +3638,14 @@
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="61" t="s">
+      <c r="J48" s="52" t="s">
         <v>54</v>
       </c>
       <c r="K48" s="17"/>
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B48, $C$2:$C$689, C48, $D$2:$D$689, D48, $E$2:$E$689, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3680,7 +3682,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B49, $C$2:$C$689, C49, $D$2:$D$689, D49, $E$2:$E$689, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P49" s="10"/>
@@ -3727,7 +3729,7 @@
         <v>500</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B50, $C$2:$C$689, C50, $D$2:$D$689, D50, $E$2:$E$689, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="10"/>
@@ -3768,7 +3770,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B51, $C$2:$C$689, C51, $D$2:$D$689, D51, $E$2:$E$689, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3800,7 +3802,7 @@
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="59" t="s">
+      <c r="J52" s="18" t="s">
         <v>40</v>
       </c>
       <c r="K52" s="18" t="s">
@@ -3814,7 +3816,7 @@
         <v>300</v>
       </c>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B52, $C$2:$C$689, C52, $D$2:$D$689, D52, $E$2:$E$689, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -3853,7 +3855,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B53, $C$2:$C$689, C53, $D$2:$D$689, D53, $E$2:$E$689, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3892,7 +3894,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B54, $C$2:$C$689, C54, $D$2:$D$689, D54, $E$2:$E$689, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -3940,7 +3942,7 @@
         <v>646</v>
       </c>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B55, $C$2:$C$689, C55, $D$2:$D$689, D55, $E$2:$E$689, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3986,7 +3988,7 @@
         <v>800.99999999999636</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B56, $C$2:$C$689, C56, $D$2:$D$689, D56, $E$2:$E$689, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P56"/>
@@ -4024,7 +4026,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B57, $C$2:$C$689, C57, $D$2:$D$689, D57, $E$2:$E$689, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -4072,7 +4074,7 @@
         <v>1008</v>
       </c>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B58, $C$2:$C$689, C58, $D$2:$D$689, D58, $E$2:$E$689, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4109,7 +4111,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B59, $C$2:$C$689, C59, $D$2:$D$689, D59, $E$2:$E$689, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="10"/>
@@ -4150,7 +4152,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B60, $C$2:$C$689, C60, $D$2:$D$689, D60, $E$2:$E$689, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -4198,7 +4200,7 @@
         <v>720</v>
       </c>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B61, $C$2:$C$689, C61, $D$2:$D$689, D61, $E$2:$E$689, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4235,56 +4237,59 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B62, $C$2:$C$689, C62, $D$2:$D$689, D62, $E$2:$E$689, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="19"/>
       <c r="P62" s="10"/>
     </row>
-    <row r="63" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="3">
+    <row r="63" spans="1:16" s="24" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="58">
         <v>46290.385416666664</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="5">
+      <c r="C63" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="60">
         <v>200</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="60">
         <v>32.49</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="61">
         <v>3.4713375800000001</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="H63" s="5">
+      <c r="H63" s="60">
         <v>31.4</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J63" s="18" t="s">
+      <c r="I63" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J63" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="K63" s="18" t="s">
+      <c r="K63" s="44" t="s">
         <v>301</v>
       </c>
-      <c r="L63" s="18">
+      <c r="L63" s="44">
         <v>6202</v>
       </c>
-      <c r="M63" s="18">
+      <c r="M63" s="44">
         <f>ABS((D63*E63)-L63)</f>
         <v>296</v>
       </c>
-      <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B63, $C$2:$C$689, C63, $D$2:$D$689, D63, $E$2:$E$689, E63) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+      <c r="N63" s="24" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="P63" s="24" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4329,7 +4334,7 @@
         <v>300</v>
       </c>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B64, $C$2:$C$689, C64, $D$2:$D$689, D64, $E$2:$E$689, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4375,7 +4380,7 @@
         <v>714</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B65, $C$2:$C$689, C65, $D$2:$D$689, D65, $E$2:$E$689, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4421,7 +4426,7 @@
         <v>350</v>
       </c>
       <c r="N66" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B66, $C$2:$C$689, C66, $D$2:$D$689, D66, $E$2:$E$689, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$689, B66, $C$2:$C$689, C66, $D$2:$D$689, D66, $E$2:$E$689, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -4467,7 +4472,7 @@
         <v>650</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B67, $C$2:$C$689, C67, $D$2:$D$689, D67, $E$2:$E$689, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="10"/>
@@ -4506,7 +4511,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B68, $C$2:$C$689, C68, $D$2:$D$689, D68, $E$2:$E$689, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="25"/>
@@ -4554,7 +4559,7 @@
         <v>200</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B69, $C$2:$C$689, C69, $D$2:$D$689, D69, $E$2:$E$689, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4600,7 +4605,7 @@
         <v>500</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B70, $C$2:$C$689, C70, $D$2:$D$689, D70, $E$2:$E$689, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4646,7 +4651,7 @@
         <v>1200</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B71, $C$2:$C$689, C71, $D$2:$D$689, D71, $E$2:$E$689, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="38" t="s">
@@ -4688,7 +4693,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B72, $C$2:$C$689, C72, $D$2:$D$689, D72, $E$2:$E$689, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -4736,7 +4741,7 @@
         <v>300</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B73, $C$2:$C$689, C73, $D$2:$D$689, D73, $E$2:$E$689, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="38" t="s">
@@ -4786,7 +4791,7 @@
         <v>360</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B74, $C$2:$C$689, C74, $D$2:$D$689, D74, $E$2:$E$689, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="38" t="s">
@@ -4829,7 +4834,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B75, $C$2:$C$689, C75, $D$2:$D$689, D75, $E$2:$E$689, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4875,7 +4880,7 @@
         <v>34175</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B76, $C$2:$C$689, C76, $D$2:$D$689, D76, $E$2:$E$689, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4911,7 +4916,7 @@
         <v>117</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B77, $C$2:$C$689, C77, $D$2:$D$689, D77, $E$2:$E$689, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4953,11 +4958,11 @@
         <v>11660</v>
       </c>
       <c r="M78" s="18">
-        <f>ABS((D78*E78)-L78)</f>
+        <f t="shared" ref="M78:M83" si="2">ABS((D78*E78)-L78)</f>
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B78, $C$2:$C$689, C78, $D$2:$D$689, D78, $E$2:$E$689, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="38" t="s">
@@ -5002,11 +5007,11 @@
         <v>3560</v>
       </c>
       <c r="M79" s="18">
-        <f>ABS((D79*E79)-L79)</f>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B79, $C$2:$C$689, C79, $D$2:$D$689, D79, $E$2:$E$689, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5049,11 +5054,11 @@
         <v>8870</v>
       </c>
       <c r="M80" s="18">
-        <f>ABS((D80*E80)-L80)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B80, $C$2:$C$689, C80, $D$2:$D$689, D80, $E$2:$E$689, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5085,7 +5090,7 @@
       <c r="I81" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="59" t="s">
+      <c r="J81" s="18" t="s">
         <v>40</v>
       </c>
       <c r="K81" s="18" t="s">
@@ -5095,11 +5100,11 @@
         <v>3430</v>
       </c>
       <c r="M81" s="18">
-        <f>ABS((D81*E81)-L81)</f>
+        <f t="shared" si="2"/>
         <v>554</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B81, $C$2:$C$689, C81, $D$2:$D$689, D81, $E$2:$E$689, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5142,11 +5147,11 @@
         <v>8970</v>
       </c>
       <c r="M82" s="18">
-        <f>ABS((D82*E82)-L82)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B82, $C$2:$C$689, C82, $D$2:$D$689, D82, $E$2:$E$689, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5188,11 +5193,11 @@
         <v>39300</v>
       </c>
       <c r="M83" s="18">
-        <f>ABS((D83*E83)-L83)</f>
+        <f t="shared" si="2"/>
         <v>18850</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B83, $C$2:$C$689, C83, $D$2:$D$689, D83, $E$2:$E$689, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5228,7 +5233,7 @@
         <v>117</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B84, $C$2:$C$689, C84, $D$2:$D$689, D84, $E$2:$E$689, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5270,11 +5275,11 @@
         <v>10250</v>
       </c>
       <c r="M85" s="18">
-        <f>ABS((D85*E85)-L85)</f>
+        <f t="shared" ref="M85:M99" si="3">ABS((D85*E85)-L85)</f>
         <v>300</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B85, $C$2:$C$689, C85, $D$2:$D$689, D85, $E$2:$E$689, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="10"/>
@@ -5318,11 +5323,11 @@
         <v>19730.5</v>
       </c>
       <c r="M86" s="27">
-        <f>ABS((D86*E86)-L86)</f>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N86" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B86, $C$2:$C$689, C86, $D$2:$D$689, D86, $E$2:$E$689, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O86" s="38" t="s">
@@ -5368,11 +5373,11 @@
         <v>19690</v>
       </c>
       <c r="M87" s="27">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N87" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B87, $C$2:$C$689, C87, $D$2:$D$689, D87, $E$2:$E$689, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O87" s="38" t="s">
@@ -5418,11 +5423,11 @@
         <v>32900</v>
       </c>
       <c r="M88" s="18">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B88, $C$2:$C$689, C88, $D$2:$D$689, D88, $E$2:$E$689, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5464,11 +5469,11 @@
         <v>8320</v>
       </c>
       <c r="M89" s="18">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B89, $C$2:$C$689, C89, $D$2:$D$689, D89, $E$2:$E$689, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5510,11 +5515,11 @@
         <v>6127.5</v>
       </c>
       <c r="M90" s="27">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="3"/>
         <v>612.5</v>
       </c>
       <c r="N90" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B90, $C$2:$C$689, C90, $D$2:$D$689, D90, $E$2:$E$689, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -5556,11 +5561,11 @@
         <v>6320</v>
       </c>
       <c r="M91" s="27">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="N91" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B91, $C$2:$C$689, C91, $D$2:$D$689, D91, $E$2:$E$689, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O91" s="29"/>
@@ -5604,11 +5609,11 @@
         <v>16755</v>
       </c>
       <c r="M92" s="18">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B92, $C$2:$C$689, C92, $D$2:$D$689, D92, $E$2:$E$689, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5650,11 +5655,11 @@
         <v>15075</v>
       </c>
       <c r="M93" s="18">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="3"/>
         <v>645</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B93, $C$2:$C$689, C93, $D$2:$D$689, D93, $E$2:$E$689, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="38" t="s">
@@ -5699,11 +5704,11 @@
         <v>6367.2</v>
       </c>
       <c r="M94" s="18">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="3"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B94, $C$2:$C$689, C94, $D$2:$D$689, D94, $E$2:$E$689, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="38" t="s">
@@ -5748,11 +5753,11 @@
         <v>9886</v>
       </c>
       <c r="M95" s="18">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="3"/>
         <v>654</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B95, $C$2:$C$689, C95, $D$2:$D$689, D95, $E$2:$E$689, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5794,11 +5799,11 @@
         <v>8420</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B96, $C$2:$C$689, C96, $D$2:$D$689, D96, $E$2:$E$689, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5840,11 +5845,11 @@
         <v>5450</v>
       </c>
       <c r="M97" s="18">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B97, $C$2:$C$689, C97, $D$2:$D$689, D97, $E$2:$E$689, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5886,11 +5891,11 @@
         <v>9170</v>
       </c>
       <c r="M98" s="27">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B98, $C$2:$C$689, C98, $D$2:$D$689, D98, $E$2:$E$689, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5932,11 +5937,11 @@
         <v>10400</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B99, $C$2:$C$689, C99, $D$2:$D$689, D99, $E$2:$E$689, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5970,7 +5975,7 @@
       </c>
       <c r="J100" s="34"/>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B100, $C$2:$C$689, C100, $D$2:$D$689, D100, $E$2:$E$689, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6016,7 +6021,7 @@
         <v>1200</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B101, $C$2:$C$689, C101, $D$2:$D$689, D101, $E$2:$E$689, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6052,7 +6057,7 @@
         <v>117</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B102, $C$2:$C$689, C102, $D$2:$D$689, D102, $E$2:$E$689, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6098,7 +6103,7 @@
         <v>280</v>
       </c>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B103, $C$2:$C$689, C103, $D$2:$D$689, D103, $E$2:$E$689, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="38" t="s">
@@ -6148,7 +6153,7 @@
         <v>250</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B104, $C$2:$C$689, C104, $D$2:$D$689, D104, $E$2:$E$689, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="10"/>
@@ -6186,7 +6191,7 @@
         <v>116</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B105, $C$2:$C$689, C105, $D$2:$D$689, D105, $E$2:$E$689, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6232,7 +6237,7 @@
         <v>18350</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B106, $C$2:$C$689, C106, $D$2:$D$689, D106, $E$2:$E$689, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6278,7 +6283,7 @@
         <v>880</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B107, $C$2:$C$689, C107, $D$2:$D$689, D107, $E$2:$E$689, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="38" t="s">
@@ -6327,7 +6332,7 @@
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B108, $C$2:$C$689, C108, $D$2:$D$689, D108, $E$2:$E$689, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6373,7 +6378,7 @@
         <v>450</v>
       </c>
       <c r="N109" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B109, $C$2:$C$689, C109, $D$2:$D$689, D109, $E$2:$E$689, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P109"/>
@@ -6420,7 +6425,7 @@
         <v>300</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B110, $C$2:$C$689, C110, $D$2:$D$689, D110, $E$2:$E$689, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6454,7 +6459,7 @@
       </c>
       <c r="J111" s="34"/>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B111, $C$2:$C$689, C111, $D$2:$D$689, D111, $E$2:$E$689, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="38" t="s">
@@ -6504,7 +6509,7 @@
         <v>660</v>
       </c>
       <c r="N112" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B112, $C$2:$C$689, C112, $D$2:$D$689, D112, $E$2:$E$689, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="24"/>
@@ -6544,7 +6549,7 @@
         <v>117</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B113, $C$2:$C$689, C113, $D$2:$D$689, D113, $E$2:$E$689, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P113"/>
@@ -6591,7 +6596,7 @@
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B114, $C$2:$C$689, C114, $D$2:$D$689, D114, $E$2:$E$689, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P114" s="19"/>
@@ -6638,7 +6643,7 @@
         <v>300</v>
       </c>
       <c r="N115" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B115, $C$2:$C$689, C115, $D$2:$D$689, D115, $E$2:$E$689, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O115"/>
@@ -6677,7 +6682,7 @@
       <c r="L116" s="18"/>
       <c r="M116" s="18"/>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B116, $C$2:$C$689, C116, $D$2:$D$689, D116, $E$2:$E$689, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -6725,7 +6730,7 @@
         <v>270</v>
       </c>
       <c r="N117" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B117, $C$2:$C$689, C117, $D$2:$D$689, D117, $E$2:$E$689, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="39" t="s">
@@ -6775,7 +6780,7 @@
         <v>188.60000000000014</v>
       </c>
       <c r="N118" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B118, $C$2:$C$689, C118, $D$2:$D$689, D118, $E$2:$E$689, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="39" t="s">
@@ -6825,7 +6830,7 @@
         <v>810</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B119, $C$2:$C$689, C119, $D$2:$D$689, D119, $E$2:$E$689, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6871,7 +6876,7 @@
         <v>850</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B120, $C$2:$C$689, C120, $D$2:$D$689, D120, $E$2:$E$689, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6908,7 +6913,7 @@
       <c r="L121" s="18"/>
       <c r="M121" s="18"/>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B121, $C$2:$C$689, C121, $D$2:$D$689, D121, $E$2:$E$689, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="10"/>
@@ -6952,11 +6957,11 @@
         <v>10300</v>
       </c>
       <c r="M122" s="18">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" ref="M122:M135" si="4">ABS((D122*E122)-L122)</f>
         <v>300</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B122, $C$2:$C$689, C122, $D$2:$D$689, D122, $E$2:$E$689, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P122" s="29"/>
@@ -6989,7 +6994,7 @@
       <c r="I123" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J123" s="59" t="s">
+      <c r="J123" s="18" t="s">
         <v>116</v>
       </c>
       <c r="K123" s="18" t="s">
@@ -6999,11 +7004,11 @@
         <v>17150</v>
       </c>
       <c r="M123" s="18">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B123, $C$2:$C$689, C123, $D$2:$D$689, D123, $E$2:$E$689, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7045,11 +7050,11 @@
         <v>8570</v>
       </c>
       <c r="M124" s="27">
-        <f>ABS((D124*E124)-L124)</f>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B124, $C$2:$C$689, C124, $D$2:$D$689, D124, $E$2:$E$689, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="38" t="s">
@@ -7094,11 +7099,11 @@
         <v>5940</v>
       </c>
       <c r="M125" s="18">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B125, $C$2:$C$689, C125, $D$2:$D$689, D125, $E$2:$E$689, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7140,11 +7145,11 @@
         <v>4200</v>
       </c>
       <c r="M126" s="18">
-        <f>ABS((D126*E126)-L126)</f>
+        <f t="shared" si="4"/>
         <v>290</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B126, $C$2:$C$689, C126, $D$2:$D$689, D126, $E$2:$E$689, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="10"/>
@@ -7188,11 +7193,11 @@
         <v>10725.5</v>
       </c>
       <c r="M127" s="18">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="4"/>
         <v>1014.5</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B127, $C$2:$C$689, C127, $D$2:$D$689, D127, $E$2:$E$689, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7234,11 +7239,11 @@
         <v>7578</v>
       </c>
       <c r="M128" s="27">
-        <f>ABS((D128*E128)-L128)</f>
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="N128" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B128, $C$2:$C$689, C128, $D$2:$D$689, D128, $E$2:$E$689, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -7280,11 +7285,11 @@
         <v>7578</v>
       </c>
       <c r="M129" s="27">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="N129" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B129, $C$2:$C$689, C129, $D$2:$D$689, D129, $E$2:$E$689, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O129" s="10"/>
@@ -7328,11 +7333,11 @@
         <v>5520</v>
       </c>
       <c r="M130" s="27">
-        <f>ABS((D130*E130)-L130)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N130" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B130, $C$2:$C$689, C130, $D$2:$D$689, D130, $E$2:$E$689, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$689, B130, $C$2:$C$689, C130, $D$2:$D$689, D130, $E$2:$E$689, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="38" t="s">
@@ -7377,11 +7382,11 @@
         <v>2657</v>
       </c>
       <c r="M131" s="27">
-        <f>ABS((D131*E131)-L131)</f>
+        <f t="shared" si="4"/>
         <v>253</v>
       </c>
       <c r="N131" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B131, $C$2:$C$689, C131, $D$2:$D$689, D131, $E$2:$E$689, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O131" s="38" t="s">
@@ -7426,11 +7431,11 @@
         <v>2554.5</v>
       </c>
       <c r="M132" s="27">
-        <f>ABS((D132*E132)-L132)</f>
+        <f t="shared" si="4"/>
         <v>355.5</v>
       </c>
       <c r="N132" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B132, $C$2:$C$689, C132, $D$2:$D$689, D132, $E$2:$E$689, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O132" s="38" t="s">
@@ -7476,11 +7481,11 @@
         <v>9170</v>
       </c>
       <c r="M133" s="27">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B133, $C$2:$C$689, C133, $D$2:$D$689, D133, $E$2:$E$689, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="38" t="s">
@@ -7525,11 +7530,11 @@
         <v>4968</v>
       </c>
       <c r="M134" s="27">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="N134" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B134, $C$2:$C$689, C134, $D$2:$D$689, D134, $E$2:$E$689, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7571,11 +7576,11 @@
         <v>10410</v>
       </c>
       <c r="M135" s="18">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B135, $C$2:$C$689, C135, $D$2:$D$689, D135, $E$2:$E$689, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P135" s="10"/>
@@ -7610,7 +7615,7 @@
       </c>
       <c r="J136" s="34"/>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B136, $C$2:$C$689, C136, $D$2:$D$689, D136, $E$2:$E$689, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="24"/>
@@ -7650,7 +7655,7 @@
         <v>143</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B137, $C$2:$C$689, C137, $D$2:$D$689, D137, $E$2:$E$689, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7696,7 +7701,7 @@
         <v>250</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B138, $C$2:$C$689, C138, $D$2:$D$689, D138, $E$2:$E$689, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7742,7 +7747,7 @@
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B139, $C$2:$C$689, C139, $D$2:$D$689, D139, $E$2:$E$689, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7776,7 +7781,7 @@
       </c>
       <c r="J140" s="34"/>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B140, $C$2:$C$689, C140, $D$2:$D$689, D140, $E$2:$E$689, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7822,7 +7827,7 @@
         <v>300</v>
       </c>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B141, $C$2:$C$689, C141, $D$2:$D$689, D141, $E$2:$E$689, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7868,7 +7873,7 @@
         <v>1400</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B142, $C$2:$C$689, C142, $D$2:$D$689, D142, $E$2:$E$689, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="38" t="s">
@@ -7917,7 +7922,7 @@
         <v>300</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B143, $C$2:$C$689, C143, $D$2:$D$689, D143, $E$2:$E$689, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7963,7 +7968,7 @@
         <v>650</v>
       </c>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B144, $C$2:$C$689, C144, $D$2:$D$689, D144, $E$2:$E$689, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8000,7 +8005,7 @@
       <c r="L145" s="18"/>
       <c r="M145" s="18"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B145, $C$2:$C$689, C145, $D$2:$D$689, D145, $E$2:$E$689, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P145" s="10"/>
@@ -8047,7 +8052,7 @@
         <v>500</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B146, $C$2:$C$689, C146, $D$2:$D$689, D146, $E$2:$E$689, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="39" t="s">
@@ -8087,7 +8092,7 @@
         <v>116</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B147, $C$2:$C$689, C147, $D$2:$D$689, D147, $E$2:$E$689, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8121,7 +8126,7 @@
       </c>
       <c r="J148" s="34"/>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B148, $C$2:$C$689, C148, $D$2:$D$689, D148, $E$2:$E$689, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8167,7 +8172,7 @@
         <v>395</v>
       </c>
       <c r="N149" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B149, $C$2:$C$689, C149, $D$2:$D$689, D149, $E$2:$E$689, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="38" t="s">
@@ -8217,7 +8222,7 @@
         <v>250</v>
       </c>
       <c r="N150" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B150, $C$2:$C$689, C150, $D$2:$D$689, D150, $E$2:$E$689, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O150" s="38" t="s">
@@ -8255,7 +8260,7 @@
       </c>
       <c r="J151" s="34"/>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B151, $C$2:$C$689, C151, $D$2:$D$689, D151, $E$2:$E$689, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8297,11 +8302,11 @@
         <v>8700</v>
       </c>
       <c r="M152" s="18">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" ref="M152:M164" si="6">ABS((D152*E152)-L152)</f>
         <v>300</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B152, $C$2:$C$689, C152, $D$2:$D$689, D152, $E$2:$E$689, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8343,11 +8348,11 @@
         <v>34100</v>
       </c>
       <c r="M153" s="18">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="6"/>
         <v>1700</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B153, $C$2:$C$689, C153, $D$2:$D$689, D153, $E$2:$E$689, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="29"/>
@@ -8390,11 +8395,11 @@
         <v>4680</v>
       </c>
       <c r="M154" s="27">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="N154" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B154, $C$2:$C$689, C154, $D$2:$D$689, D154, $E$2:$E$689, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="P154" s="29"/>
@@ -8437,11 +8442,11 @@
         <v>4520</v>
       </c>
       <c r="M155" s="27">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N155" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B155, $C$2:$C$689, C155, $D$2:$D$689, D155, $E$2:$E$689, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8483,11 +8488,11 @@
         <v>14100</v>
       </c>
       <c r="M156" s="18">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B156, $C$2:$C$689, C156, $D$2:$D$689, D156, $E$2:$E$689, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8529,11 +8534,11 @@
         <v>5755</v>
       </c>
       <c r="M157" s="27">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="6"/>
         <v>275</v>
       </c>
       <c r="N157" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B157, $C$2:$C$689, C157, $D$2:$D$689, D157, $E$2:$E$689, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O157" s="10"/>
@@ -8577,11 +8582,11 @@
         <v>5805</v>
       </c>
       <c r="M158" s="27">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="6"/>
         <v>225</v>
       </c>
       <c r="N158" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B158, $C$2:$C$689, C158, $D$2:$D$689, D158, $E$2:$E$689, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8623,11 +8628,11 @@
         <v>8820</v>
       </c>
       <c r="M159" s="27">
-        <f>ABS((D159*E159)-L159)</f>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
       <c r="N159" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B159, $C$2:$C$689, C159, $D$2:$D$689, D159, $E$2:$E$689, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="29"/>
@@ -8671,11 +8676,11 @@
         <v>36946</v>
       </c>
       <c r="M160" s="27">
-        <f>ABS((D160*E160)-L160)</f>
+        <f t="shared" si="6"/>
         <v>934</v>
       </c>
       <c r="N160" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B160, $C$2:$C$689, C160, $D$2:$D$689, D160, $E$2:$E$689, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="29"/>
@@ -8719,11 +8724,11 @@
         <v>10814</v>
       </c>
       <c r="M161" s="18">
-        <f>ABS((D161*E161)-L161)</f>
+        <f t="shared" si="6"/>
         <v>501</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B161, $C$2:$C$689, C161, $D$2:$D$689, D161, $E$2:$E$689, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="38" t="s">
@@ -8768,11 +8773,11 @@
         <v>14440</v>
       </c>
       <c r="M162" s="18">
-        <f>ABS((D162*E162)-L162)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B162, $C$2:$C$689, C162, $D$2:$D$689, D162, $E$2:$E$689, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O162"/>
@@ -8816,11 +8821,11 @@
         <v>5180</v>
       </c>
       <c r="M163" s="26">
-        <f>ABS((D163*E163)-L163)</f>
+        <f t="shared" si="6"/>
         <v>268</v>
       </c>
       <c r="N163" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B163, $C$2:$C$689, C163, $D$2:$D$689, D163, $E$2:$E$689, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8862,11 +8867,11 @@
         <v>5120</v>
       </c>
       <c r="M164" s="18">
-        <f>ABS((D164*E164)-L164)</f>
+        <f t="shared" si="6"/>
         <v>260</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B164, $C$2:$C$689, C164, $D$2:$D$689, D164, $E$2:$E$689, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8902,7 +8907,7 @@
         <v>116</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B165, $C$2:$C$689, C165, $D$2:$D$689, D165, $E$2:$E$689, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8948,7 +8953,7 @@
         <v>320</v>
       </c>
       <c r="N166" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B166, $C$2:$C$689, C166, $D$2:$D$689, D166, $E$2:$E$689, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="29"/>
@@ -8996,7 +9001,7 @@
         <v>235</v>
       </c>
       <c r="N167" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B167, $C$2:$C$689, C167, $D$2:$D$689, D167, $E$2:$E$689, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O167" s="29"/>
@@ -9044,7 +9049,7 @@
         <v>376</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B168, $C$2:$C$689, C168, $D$2:$D$689, D168, $E$2:$E$689, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9078,7 +9083,7 @@
       </c>
       <c r="J169" s="34"/>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B169, $C$2:$C$689, C169, $D$2:$D$689, D169, $E$2:$E$689, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9114,7 +9119,7 @@
         <v>116</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B170, $C$2:$C$689, C170, $D$2:$D$689, D170, $E$2:$E$689, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9160,7 +9165,7 @@
         <v>420</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B171, $C$2:$C$689, C171, $D$2:$D$689, D171, $E$2:$E$689, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9194,7 +9199,7 @@
       </c>
       <c r="J172" s="34"/>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B172, $C$2:$C$689, C172, $D$2:$D$689, D172, $E$2:$E$689, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9240,7 +9245,7 @@
         <v>500</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B173, $C$2:$C$689, C173, $D$2:$D$689, D173, $E$2:$E$689, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9274,7 +9279,7 @@
       </c>
       <c r="J174" s="34"/>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B174, $C$2:$C$689, C174, $D$2:$D$689, D174, $E$2:$E$689, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P174" s="29"/>
@@ -9311,7 +9316,7 @@
         <v>117</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B175, $C$2:$C$689, C175, $D$2:$D$689, D175, $E$2:$E$689, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9347,7 +9352,7 @@
         <v>193</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B176, $C$2:$C$689, C176, $D$2:$D$689, D176, $E$2:$E$689, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9383,7 +9388,7 @@
         <v>117</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B177, $C$2:$C$689, C177, $D$2:$D$689, D177, $E$2:$E$689, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="38" t="s">
@@ -9425,7 +9430,7 @@
       <c r="L178" s="17"/>
       <c r="M178" s="17"/>
       <c r="N178" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B178, $C$2:$C$689, C178, $D$2:$D$689, D178, $E$2:$E$689, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9461,7 +9466,7 @@
         <v>116</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B179, $C$2:$C$689, C179, $D$2:$D$689, D179, $E$2:$E$689, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9507,7 +9512,7 @@
         <v>527.5</v>
       </c>
       <c r="N180" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B180, $C$2:$C$689, C180, $D$2:$D$689, D180, $E$2:$E$689, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="29"/>
@@ -9555,7 +9560,7 @@
         <v>300</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B181, $C$2:$C$689, C181, $D$2:$D$689, D181, $E$2:$E$689, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="38" t="s">
@@ -9599,7 +9604,7 @@
       <c r="L182" s="27"/>
       <c r="M182" s="27"/>
       <c r="N182" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B182, $C$2:$C$689, C182, $D$2:$D$689, D182, $E$2:$E$689, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="29"/>
@@ -9637,7 +9642,7 @@
         <v>117</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B183, $C$2:$C$689, C183, $D$2:$D$689, D183, $E$2:$E$689, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9683,7 +9688,7 @@
         <v>1000</v>
       </c>
       <c r="N184" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B184, $C$2:$C$689, C184, $D$2:$D$689, D184, $E$2:$E$689, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P184" s="29"/>
@@ -9720,7 +9725,7 @@
         <v>116</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B185, $C$2:$C$689, C185, $D$2:$D$689, D185, $E$2:$E$689, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9766,7 +9771,7 @@
         <v>250</v>
       </c>
       <c r="N186" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B186, $C$2:$C$689, C186, $D$2:$D$689, D186, $E$2:$E$689, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9812,7 +9817,7 @@
         <v>646</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B187, $C$2:$C$689, C187, $D$2:$D$689, D187, $E$2:$E$689, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="38" t="s">
@@ -9861,7 +9866,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B188, $C$2:$C$689, C188, $D$2:$D$689, D188, $E$2:$E$689, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9895,7 +9900,7 @@
       </c>
       <c r="J189" s="34"/>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B189, $C$2:$C$689, C189, $D$2:$D$689, D189, $E$2:$E$689, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9941,7 +9946,7 @@
         <v>250</v>
       </c>
       <c r="N190" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B190, $C$2:$C$689, C190, $D$2:$D$689, D190, $E$2:$E$689, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="10"/>
@@ -9989,7 +9994,7 @@
         <v>500</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B191, $C$2:$C$689, C191, $D$2:$D$689, D191, $E$2:$E$689, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10028,7 +10033,7 @@
       <c r="L192" s="44"/>
       <c r="M192" s="44"/>
       <c r="N192" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B192, $C$2:$C$689, C192, $D$2:$D$689, D192, $E$2:$E$689, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="24"/>
@@ -10078,7 +10083,7 @@
         <v>300</v>
       </c>
       <c r="N193" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B193, $C$2:$C$689, C193, $D$2:$D$689, D193, $E$2:$E$689, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="29"/>
@@ -10126,7 +10131,7 @@
         <v>188</v>
       </c>
       <c r="N194" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B194, $C$2:$C$689, C194, $D$2:$D$689, D194, $E$2:$E$689, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$689, B194, $C$2:$C$689, C194, $D$2:$D$689, D194, $E$2:$E$689, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="29"/>
@@ -10174,7 +10179,7 @@
         <v>275</v>
       </c>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B195, $C$2:$C$689, C195, $D$2:$D$689, D195, $E$2:$E$689, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10210,7 +10215,7 @@
         <v>117</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B196, $C$2:$C$689, C196, $D$2:$D$689, D196, $E$2:$E$689, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10256,7 +10261,7 @@
         <v>800</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B197, $C$2:$C$689, C197, $D$2:$D$689, D197, $E$2:$E$689, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10292,7 +10297,7 @@
         <v>117</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B198, $C$2:$C$689, C198, $D$2:$D$689, D198, $E$2:$E$689, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10331,7 +10336,7 @@
       <c r="L199" s="17"/>
       <c r="M199" s="17"/>
       <c r="N199" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B199, $C$2:$C$689, C199, $D$2:$D$689, D199, $E$2:$E$689, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P199" s="24"/>
@@ -10378,7 +10383,7 @@
         <v>300</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B200, $C$2:$C$689, C200, $D$2:$D$689, D200, $E$2:$E$689, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10414,7 +10419,7 @@
         <v>116</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B201, $C$2:$C$689, C201, $D$2:$D$689, D201, $E$2:$E$689, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10460,7 +10465,7 @@
         <v>940</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B202, $C$2:$C$689, C202, $D$2:$D$689, D202, $E$2:$E$689, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10506,7 +10511,7 @@
         <v>290</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B203, $C$2:$C$689, C203, $D$2:$D$689, D203, $E$2:$E$689, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10552,7 +10557,7 @@
         <v>800</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B204, $C$2:$C$689, C204, $D$2:$D$689, D204, $E$2:$E$689, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="38" t="s">
@@ -10591,7 +10596,7 @@
         <v>117</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B205, $C$2:$C$689, C205, $D$2:$D$689, D205, $E$2:$E$689, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10637,7 +10642,7 @@
         <v>450</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B206, $C$2:$C$689, C206, $D$2:$D$689, D206, $E$2:$E$689, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10673,7 +10678,7 @@
         <v>116</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B207, $C$2:$C$689, C207, $D$2:$D$689, D207, $E$2:$E$689, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10719,7 +10724,7 @@
         <v>320</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B208, $C$2:$C$689, C208, $D$2:$D$689, D208, $E$2:$E$689, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10765,7 +10770,7 @@
         <v>448</v>
       </c>
       <c r="N209" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B209, $C$2:$C$689, C209, $D$2:$D$689, D209, $E$2:$E$689, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10811,7 +10816,7 @@
         <v>650</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B210, $C$2:$C$689, C210, $D$2:$D$689, D210, $E$2:$E$689, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="29"/>
@@ -10858,7 +10863,7 @@
         <v>150</v>
       </c>
       <c r="N211" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B211, $C$2:$C$689, C211, $D$2:$D$689, D211, $E$2:$E$689, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10904,7 +10909,7 @@
         <v>250</v>
       </c>
       <c r="N212" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B212, $C$2:$C$689, C212, $D$2:$D$689, D212, $E$2:$E$689, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10940,7 +10945,7 @@
         <v>117</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B213, $C$2:$C$689, C213, $D$2:$D$689, D213, $E$2:$E$689, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10974,7 +10979,7 @@
       </c>
       <c r="J214" s="34"/>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B214, $C$2:$C$689, C214, $D$2:$D$689, D214, $E$2:$E$689, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11010,7 +11015,7 @@
         <v>117</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B215, $C$2:$C$689, C215, $D$2:$D$689, D215, $E$2:$E$689, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="29"/>
@@ -11057,7 +11062,7 @@
         <v>650</v>
       </c>
       <c r="N216" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B216, $C$2:$C$689, C216, $D$2:$D$689, D216, $E$2:$E$689, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P216" s="29"/>
@@ -11094,7 +11099,7 @@
         <v>116</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B217, $C$2:$C$689, C217, $D$2:$D$689, D217, $E$2:$E$689, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P217" s="29"/>
@@ -11131,7 +11136,7 @@
         <v>54</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B218, $C$2:$C$689, C218, $D$2:$D$689, D218, $E$2:$E$689, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11177,7 +11182,7 @@
         <v>360</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B219, $C$2:$C$689, C219, $D$2:$D$689, D219, $E$2:$E$689, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11223,7 +11228,7 @@
         <v>816</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B220, $C$2:$C$689, C220, $D$2:$D$689, D220, $E$2:$E$689, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11269,7 +11274,7 @@
         <v>300</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B221, $C$2:$C$689, C221, $D$2:$D$689, D221, $E$2:$E$689, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P221" s="25"/>
@@ -11306,7 +11311,7 @@
         <v>117</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B222, $C$2:$C$689, C222, $D$2:$D$689, D222, $E$2:$E$689, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="29"/>
@@ -11341,7 +11346,7 @@
       </c>
       <c r="J223" s="34"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B223, $C$2:$C$689, C223, $D$2:$D$689, D223, $E$2:$E$689, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11375,7 +11380,7 @@
       </c>
       <c r="J224" s="34"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B224, $C$2:$C$689, C224, $D$2:$D$689, D224, $E$2:$E$689, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11411,7 +11416,7 @@
         <v>54</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B225, $C$2:$C$689, C225, $D$2:$D$689, D225, $E$2:$E$689, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11457,7 +11462,7 @@
         <v>250</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B226, $C$2:$C$689, C226, $D$2:$D$689, D226, $E$2:$E$689, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11503,7 +11508,7 @@
         <v>48320</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B227, $C$2:$C$689, C227, $D$2:$D$689, D227, $E$2:$E$689, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="38" t="s">
@@ -11552,7 +11557,7 @@
         <v>300</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B228, $C$2:$C$689, C228, $D$2:$D$689, D228, $E$2:$E$689, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="10"/>
@@ -11591,7 +11596,7 @@
       <c r="L229" s="18"/>
       <c r="M229" s="18"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B229, $C$2:$C$689, C229, $D$2:$D$689, D229, $E$2:$E$689, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="10"/>
@@ -11639,7 +11644,7 @@
         <v>651</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B230, $C$2:$C$689, C230, $D$2:$D$689, D230, $E$2:$E$689, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11685,7 +11690,7 @@
         <v>650</v>
       </c>
       <c r="N231" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B231, $C$2:$C$689, C231, $D$2:$D$689, D231, $E$2:$E$689, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P231" s="29"/>
@@ -11722,7 +11727,7 @@
         <v>117</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B232, $C$2:$C$689, C232, $D$2:$D$689, D232, $E$2:$E$689, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11756,7 +11761,7 @@
       </c>
       <c r="J233" s="34"/>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B233, $C$2:$C$689, C233, $D$2:$D$689, D233, $E$2:$E$689, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11790,7 +11795,7 @@
       </c>
       <c r="J234" s="34"/>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B234, $C$2:$C$689, C234, $D$2:$D$689, D234, $E$2:$E$689, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11836,7 +11841,7 @@
         <v>450</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B235, $C$2:$C$689, C235, $D$2:$D$689, D235, $E$2:$E$689, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11882,7 +11887,7 @@
         <v>300</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B236, $C$2:$C$689, C236, $D$2:$D$689, D236, $E$2:$E$689, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11921,7 +11926,7 @@
         <v>144</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B237, $C$2:$C$689, C237, $D$2:$D$689, D237, $E$2:$E$689, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11967,7 +11972,7 @@
         <v>400</v>
       </c>
       <c r="N238" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B238, $C$2:$C$689, C238, $D$2:$D$689, D238, $E$2:$E$689, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12003,7 +12008,7 @@
         <v>117</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B239, $C$2:$C$689, C239, $D$2:$D$689, D239, $E$2:$E$689, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="29"/>
@@ -12040,7 +12045,7 @@
         <v>116</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B240, $C$2:$C$689, C240, $D$2:$D$689, D240, $E$2:$E$689, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12077,7 +12082,7 @@
       <c r="L241" s="18"/>
       <c r="M241" s="18"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B241, $C$2:$C$689, C241, $D$2:$D$689, D241, $E$2:$E$689, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="10"/>
@@ -12125,7 +12130,7 @@
         <v>250</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B242, $C$2:$C$689, C242, $D$2:$D$689, D242, $E$2:$E$689, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P242" s="29"/>
@@ -12160,7 +12165,7 @@
       </c>
       <c r="J243" s="34"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B243, $C$2:$C$689, C243, $D$2:$D$689, D243, $E$2:$E$689, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12194,7 +12199,7 @@
       </c>
       <c r="J244" s="34"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B244, $C$2:$C$689, C244, $D$2:$D$689, D244, $E$2:$E$689, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12240,7 +12245,7 @@
         <v>480</v>
       </c>
       <c r="N245" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B245, $C$2:$C$689, C245, $D$2:$D$689, D245, $E$2:$E$689, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -12288,7 +12293,7 @@
         <v>47900</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B246, $C$2:$C$689, C246, $D$2:$D$689, D246, $E$2:$E$689, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="38" t="s">
@@ -12327,7 +12332,7 @@
         <v>117</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B247, $C$2:$C$689, C247, $D$2:$D$689, D247, $E$2:$E$689, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12373,7 +12378,7 @@
         <v>370</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B248, $C$2:$C$689, C248, $D$2:$D$689, D248, $E$2:$E$689, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P248" s="29"/>
@@ -12420,7 +12425,7 @@
         <v>650</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B249, $C$2:$C$689, C249, $D$2:$D$689, D249, $E$2:$E$689, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="38" t="s">
@@ -12469,7 +12474,7 @@
         <v>495</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B250, $C$2:$C$689, C250, $D$2:$D$689, D250, $E$2:$E$689, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="38" t="s">
@@ -12519,7 +12524,7 @@
         <v>300</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B251, $C$2:$C$689, C251, $D$2:$D$689, D251, $E$2:$E$689, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="10"/>
@@ -12557,7 +12562,7 @@
         <v>117</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B252, $C$2:$C$689, C252, $D$2:$D$689, D252, $E$2:$E$689, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12603,7 +12608,7 @@
         <v>235</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B253, $C$2:$C$689, C253, $D$2:$D$689, D253, $E$2:$E$689, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12642,7 +12647,7 @@
       <c r="L254" s="18"/>
       <c r="M254" s="18"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B254, $C$2:$C$689, C254, $D$2:$D$689, D254, $E$2:$E$689, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="10"/>
@@ -12690,7 +12695,7 @@
         <v>260</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B255, $C$2:$C$689, C255, $D$2:$D$689, D255, $E$2:$E$689, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12736,7 +12741,7 @@
         <v>300</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B256, $C$2:$C$689, C256, $D$2:$D$689, D256, $E$2:$E$689, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="38" t="s">
@@ -12779,7 +12784,7 @@
       <c r="L257" s="18"/>
       <c r="M257" s="18"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B257, $C$2:$C$689, C257, $D$2:$D$689, D257, $E$2:$E$689, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="10"/>
@@ -12818,7 +12823,7 @@
       <c r="L258" s="18"/>
       <c r="M258" s="18"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B258, $C$2:$C$689, C258, $D$2:$D$689, D258, $E$2:$E$689, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N301" si="8">IF(COUNTIFS( $B$2:$B$689, B258, $C$2:$C$689, C258, $D$2:$D$689, D258, $E$2:$E$689, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P258" s="10"/>
@@ -12855,7 +12860,7 @@
         <v>116</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B259, $C$2:$C$689, C259, $D$2:$D$689, D259, $E$2:$E$689, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12901,7 +12906,7 @@
         <v>1800</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B260, $C$2:$C$689, C260, $D$2:$D$689, D260, $E$2:$E$689, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12947,7 +12952,7 @@
         <v>500</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B261, $C$2:$C$689, C261, $D$2:$D$689, D261, $E$2:$E$689, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="38" t="s">
@@ -12996,7 +13001,7 @@
         <v>650</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B262, $C$2:$C$689, C262, $D$2:$D$689, D262, $E$2:$E$689, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O262"/>
@@ -13044,7 +13049,7 @@
         <v>300</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B263, $C$2:$C$689, C263, $D$2:$D$689, D263, $E$2:$E$689, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13090,7 +13095,7 @@
         <v>47480</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B264, $C$2:$C$689, C264, $D$2:$D$689, D264, $E$2:$E$689, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13124,7 +13129,7 @@
       </c>
       <c r="J265" s="34"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B265, $C$2:$C$689, C265, $D$2:$D$689, D265, $E$2:$E$689, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="29"/>
@@ -13171,7 +13176,7 @@
         <v>340</v>
       </c>
       <c r="N266" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B266, $C$2:$C$689, C266, $D$2:$D$689, D266, $E$2:$E$689, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13207,7 +13212,7 @@
         <v>116</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B267, $C$2:$C$689, C267, $D$2:$D$689, D267, $E$2:$E$689, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13253,7 +13258,7 @@
         <v>300</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B268, $C$2:$C$689, C268, $D$2:$D$689, D268, $E$2:$E$689, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13289,7 +13294,7 @@
         <v>116</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B269, $C$2:$C$689, C269, $D$2:$D$689, D269, $E$2:$E$689, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13335,7 +13340,7 @@
         <v>300</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B270, $C$2:$C$689, C270, $D$2:$D$689, D270, $E$2:$E$689, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13371,7 +13376,7 @@
         <v>117</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B271, $C$2:$C$689, C271, $D$2:$D$689, D271, $E$2:$E$689, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13407,7 +13412,7 @@
         <v>116</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B272, $C$2:$C$689, C272, $D$2:$D$689, D272, $E$2:$E$689, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13448,7 +13453,7 @@
       <c r="L273" s="17"/>
       <c r="M273" s="17"/>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B273, $C$2:$C$689, C273, $D$2:$D$689, D273, $E$2:$E$689, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13485,7 +13490,7 @@
       <c r="L274" s="18"/>
       <c r="M274" s="18"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B274, $C$2:$C$689, C274, $D$2:$D$689, D274, $E$2:$E$689, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="10"/>
@@ -13526,7 +13531,7 @@
       <c r="L275" s="18"/>
       <c r="M275" s="18"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B275, $C$2:$C$689, C275, $D$2:$D$689, D275, $E$2:$E$689, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="10"/>
@@ -13562,7 +13567,7 @@
       </c>
       <c r="J276" s="34"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B276, $C$2:$C$689, C276, $D$2:$D$689, D276, $E$2:$E$689, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P276" s="29"/>
@@ -13609,7 +13614,7 @@
         <v>300</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B277, $C$2:$C$689, C277, $D$2:$D$689, D277, $E$2:$E$689, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13655,7 +13660,7 @@
         <v>300</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B278, $C$2:$C$689, C278, $D$2:$D$689, D278, $E$2:$E$689, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13691,7 +13696,7 @@
         <v>152</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B279, $C$2:$C$689, C279, $D$2:$D$689, D279, $E$2:$E$689, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13737,7 +13742,7 @@
         <v>285</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B280, $C$2:$C$689, C280, $D$2:$D$689, D280, $E$2:$E$689, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13783,7 +13788,7 @@
         <v>726</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B281, $C$2:$C$689, C281, $D$2:$D$689, D281, $E$2:$E$689, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13817,7 +13822,7 @@
       </c>
       <c r="J282" s="34"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B282, $C$2:$C$689, C282, $D$2:$D$689, D282, $E$2:$E$689, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13853,7 +13858,7 @@
         <v>116</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B283, $C$2:$C$689, C283, $D$2:$D$689, D283, $E$2:$E$689, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13887,7 +13892,7 @@
       </c>
       <c r="J284" s="34"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B284, $C$2:$C$689, C284, $D$2:$D$689, D284, $E$2:$E$689, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P284" s="29"/>
@@ -13922,7 +13927,7 @@
       </c>
       <c r="J285" s="34"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B285, $C$2:$C$689, C285, $D$2:$D$689, D285, $E$2:$E$689, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13968,7 +13973,7 @@
         <v>275</v>
       </c>
       <c r="N286" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B286, $C$2:$C$689, C286, $D$2:$D$689, D286, $E$2:$E$689, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14014,7 +14019,7 @@
         <v>250</v>
       </c>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B287, $C$2:$C$689, C287, $D$2:$D$689, D287, $E$2:$E$689, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P287" s="29"/>
@@ -14049,7 +14054,7 @@
       </c>
       <c r="J288" s="34"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B288, $C$2:$C$689, C288, $D$2:$D$689, D288, $E$2:$E$689, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14083,7 +14088,7 @@
       </c>
       <c r="J289" s="34"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B289, $C$2:$C$689, C289, $D$2:$D$689, D289, $E$2:$E$689, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14129,7 +14134,7 @@
         <v>300</v>
       </c>
       <c r="N290" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B290, $C$2:$C$689, C290, $D$2:$D$689, D290, $E$2:$E$689, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14165,7 +14170,7 @@
         <v>54</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B291, $C$2:$C$689, C291, $D$2:$D$689, D291, $E$2:$E$689, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14199,7 +14204,7 @@
       </c>
       <c r="J292" s="34"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B292, $C$2:$C$689, C292, $D$2:$D$689, D292, $E$2:$E$689, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14245,7 +14250,7 @@
         <v>250</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B293, $C$2:$C$689, C293, $D$2:$D$689, D293, $E$2:$E$689, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14281,7 +14286,7 @@
         <v>117</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B294, $C$2:$C$689, C294, $D$2:$D$689, D294, $E$2:$E$689, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14317,7 +14322,7 @@
         <v>117</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B295, $C$2:$C$689, C295, $D$2:$D$689, D295, $E$2:$E$689, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14353,7 +14358,7 @@
         <v>117</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B296, $C$2:$C$689, C296, $D$2:$D$689, D296, $E$2:$E$689, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14399,7 +14404,7 @@
         <v>250</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B297, $C$2:$C$689, C297, $D$2:$D$689, D297, $E$2:$E$689, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O297" s="10"/>
@@ -14435,7 +14440,7 @@
       </c>
       <c r="J298" s="34"/>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B298, $C$2:$C$689, C298, $D$2:$D$689, D298, $E$2:$E$689, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14474,7 +14479,7 @@
       <c r="L299" s="27"/>
       <c r="M299" s="27"/>
       <c r="N299" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B299, $C$2:$C$689, C299, $D$2:$D$689, D299, $E$2:$E$689, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14513,7 +14518,7 @@
       <c r="L300" s="27"/>
       <c r="M300" s="27"/>
       <c r="N300" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B300, $C$2:$C$689, C300, $D$2:$D$689, D300, $E$2:$E$689, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O300" s="29"/>
@@ -14551,7 +14556,7 @@
         <v>116</v>
       </c>
       <c r="N301" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B301, $C$2:$C$689, C301, $D$2:$D$689, D301, $E$2:$E$689, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22255,7 +22260,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B2, $C$2:$C$689, C2, $D$2:$D$689, D2, $E$2:$E$689, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$689, B2, $C$2:$C$689, C2, $D$2:$D$689, D2, $E$2:$E$689, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -22301,7 +22306,7 @@
         <v>10880</v>
       </c>
       <c r="N3" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B3, $C$2:$C$689, C3, $D$2:$D$689, D3, $E$2:$E$689, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22342,7 +22347,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B4, $C$2:$C$689, C4, $D$2:$D$689, D4, $E$2:$E$689, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22388,7 +22393,7 @@
         <v>10680</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B5, $C$2:$C$689, C5, $D$2:$D$689, D5, $E$2:$E$689, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22429,7 +22434,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B6, $C$2:$C$689, C6, $D$2:$D$689, D6, $E$2:$E$689, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22466,7 +22471,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B7, $C$2:$C$689, C7, $D$2:$D$689, D7, $E$2:$E$689, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22505,7 +22510,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B8, $C$2:$C$689, C8, $D$2:$D$689, D8, $E$2:$E$689, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22544,7 +22549,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B9, $C$2:$C$689, C9, $D$2:$D$689, D9, $E$2:$E$689, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22583,7 +22588,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B10, $C$2:$C$689, C10, $D$2:$D$689, D10, $E$2:$E$689, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22620,7 +22625,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B11, $C$2:$C$689, C11, $D$2:$D$689, D11, $E$2:$E$689, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22662,7 +22667,7 @@
         <v>3156</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B12, $C$2:$C$689, C12, $D$2:$D$689, D12, $E$2:$E$689, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -22701,7 +22706,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B13, $C$2:$C$689, C13, $D$2:$D$689, D13, $E$2:$E$689, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22738,7 +22743,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B14, $C$2:$C$689, C14, $D$2:$D$689, D14, $E$2:$E$689, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14"/>
@@ -22777,7 +22782,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B15, $C$2:$C$689, C15, $D$2:$D$689, D15, $E$2:$E$689, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15"/>
@@ -22816,7 +22821,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B16, $C$2:$C$689, C16, $D$2:$D$689, D16, $E$2:$E$689, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16"/>
@@ -22864,7 +22869,7 @@
         <v>240</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B17, $C$2:$C$689, C17, $D$2:$D$689, D17, $E$2:$E$689, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22901,7 +22906,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B18, $C$2:$C$689, C18, $D$2:$D$689, D18, $E$2:$E$689, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18"/>
@@ -22940,7 +22945,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B19, $C$2:$C$689, C19, $D$2:$D$689, D19, $E$2:$E$689, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -22981,7 +22986,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B20, $C$2:$C$689, C20, $D$2:$D$689, D20, $E$2:$E$689, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -23020,7 +23025,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B21, $C$2:$C$689, C21, $D$2:$D$689, D21, $E$2:$E$689, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21"/>
@@ -23068,7 +23073,7 @@
         <v>295</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B22, $C$2:$C$689, C22, $D$2:$D$689, D22, $E$2:$E$689, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23109,7 +23114,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B23, $C$2:$C$689, C23, $D$2:$D$689, D23, $E$2:$E$689, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -23148,7 +23153,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B24, $C$2:$C$689, C24, $D$2:$D$689, D24, $E$2:$E$689, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -23187,7 +23192,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B25, $C$2:$C$689, C25, $D$2:$D$689, D25, $E$2:$E$689, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
@@ -23228,7 +23233,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B26, $C$2:$C$689, C26, $D$2:$D$689, D26, $E$2:$E$689, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -23269,7 +23274,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B27, $C$2:$C$689, C27, $D$2:$D$689, D27, $E$2:$E$689, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P27"/>
@@ -23307,7 +23312,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B28, $C$2:$C$689, C28, $D$2:$D$689, D28, $E$2:$E$689, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -23355,7 +23360,7 @@
         <v>300</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B29, $C$2:$C$689, C29, $D$2:$D$689, D29, $E$2:$E$689, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -23404,7 +23409,7 @@
         <v>225</v>
       </c>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B30, $C$2:$C$689, C30, $D$2:$D$689, D30, $E$2:$E$689, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23443,7 +23448,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B31, $C$2:$C$689, C31, $D$2:$D$689, D31, $E$2:$E$689, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -23482,7 +23487,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B32, $C$2:$C$689, C32, $D$2:$D$689, D32, $E$2:$E$689, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -23522,7 +23527,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B33, $C$2:$C$689, C33, $D$2:$D$689, D33, $E$2:$E$689, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -23561,7 +23566,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B34, $C$2:$C$689, C34, $D$2:$D$689, D34, $E$2:$E$689, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -23610,7 +23615,7 @@
         <v>540</v>
       </c>
       <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B35, $C$2:$C$689, C35, $D$2:$D$689, D35, $E$2:$E$689, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -23651,7 +23656,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B36, $C$2:$C$689, C36, $D$2:$D$689, D36, $E$2:$E$689, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -23692,7 +23697,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B37, $C$2:$C$689, C37, $D$2:$D$689, D37, $E$2:$E$689, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -23740,7 +23745,7 @@
         <v>300</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B38, $C$2:$C$689, C38, $D$2:$D$689, D38, $E$2:$E$689, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P38" s="24"/>
@@ -23787,7 +23792,7 @@
         <v>516</v>
       </c>
       <c r="N39" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B39, $C$2:$C$689, C39, $D$2:$D$689, D39, $E$2:$E$689, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23824,7 +23829,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B40, $C$2:$C$689, C40, $D$2:$D$689, D40, $E$2:$E$689, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -23872,7 +23877,7 @@
         <v>554</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B41, $C$2:$C$689, C41, $D$2:$D$689, D41, $E$2:$E$689, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23911,7 +23916,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B42, $C$2:$C$689, C42, $D$2:$D$689, D42, $E$2:$E$689, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42" s="10"/>
@@ -23952,7 +23957,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B43, $C$2:$C$689, C43, $D$2:$D$689, D43, $E$2:$E$689, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="10"/>
@@ -24000,7 +24005,7 @@
         <v>300</v>
       </c>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B44, $C$2:$C$689, C44, $D$2:$D$689, D44, $E$2:$E$689, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24039,7 +24044,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B45, $C$2:$C$689, C45, $D$2:$D$689, D45, $E$2:$E$689, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -24080,7 +24085,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B46, $C$2:$C$689, C46, $D$2:$D$689, D46, $E$2:$E$689, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24117,7 +24122,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B47, $C$2:$C$689, C47, $D$2:$D$689, D47, $E$2:$E$689, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P47" s="10"/>
@@ -24157,7 +24162,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B48, $C$2:$C$689, C48, $D$2:$D$689, D48, $E$2:$E$689, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="10"/>
@@ -24205,7 +24210,7 @@
         <v>646</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B49, $C$2:$C$689, C49, $D$2:$D$689, D49, $E$2:$E$689, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="10"/>
@@ -24246,7 +24251,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B50, $C$2:$C$689, C50, $D$2:$D$689, D50, $E$2:$E$689, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24292,7 +24297,7 @@
         <v>500</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B51, $C$2:$C$689, C51, $D$2:$D$689, D51, $E$2:$E$689, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="10"/>
@@ -24333,7 +24338,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B52, $C$2:$C$689, C52, $D$2:$D$689, D52, $E$2:$E$689, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -24372,7 +24377,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B53, $C$2:$C$689, C53, $D$2:$D$689, D53, $E$2:$E$689, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24409,7 +24414,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B54, $C$2:$C$689, C54, $D$2:$D$689, D54, $E$2:$E$689, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -24457,7 +24462,7 @@
         <v>296</v>
       </c>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B55, $C$2:$C$689, C55, $D$2:$D$689, D55, $E$2:$E$689, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24503,7 +24508,7 @@
         <v>350</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B56, $C$2:$C$689, C56, $D$2:$D$689, D56, $E$2:$E$689, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24540,7 +24545,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B57, $C$2:$C$689, C57, $D$2:$D$689, D57, $E$2:$E$689, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24586,7 +24591,7 @@
         <v>650</v>
       </c>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B58, $C$2:$C$689, C58, $D$2:$D$689, D58, $E$2:$E$689, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24625,7 +24630,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B59, $C$2:$C$689, C59, $D$2:$D$689, D59, $E$2:$E$689, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -24664,7 +24669,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B60, $C$2:$C$689, C60, $D$2:$D$689, D60, $E$2:$E$689, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="19"/>
@@ -24704,7 +24709,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B61, $C$2:$C$689, C61, $D$2:$D$689, D61, $E$2:$E$689, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P61" s="25"/>
@@ -24744,7 +24749,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B62, $C$2:$C$689, C62, $D$2:$D$689, D62, $E$2:$E$689, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -24783,7 +24788,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B63, $C$2:$C$689, C63, $D$2:$D$689, D63, $E$2:$E$689, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="25"/>
@@ -24823,7 +24828,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B64, $C$2:$C$689, C64, $D$2:$D$689, D64, $E$2:$E$689, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24865,11 +24870,11 @@
         <v>32400</v>
       </c>
       <c r="M65" s="18">
-        <f t="shared" ref="M65:M75" si="0">ABS((D65*E65)-L65)</f>
+        <f t="shared" ref="M65:M75" si="1">ABS((D65*E65)-L65)</f>
         <v>500</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B65, $C$2:$C$689, C65, $D$2:$D$689, D65, $E$2:$E$689, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24911,11 +24916,11 @@
         <v>11360</v>
       </c>
       <c r="M66" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N66" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B66, $C$2:$C$689, C66, $D$2:$D$689, D66, $E$2:$E$689, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="2">IF(COUNTIFS( $B$2:$B$689, B66, $C$2:$C$689, C66, $D$2:$D$689, D66, $E$2:$E$689, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -24957,11 +24962,11 @@
         <v>3560</v>
       </c>
       <c r="M67" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>250</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B67, $C$2:$C$689, C67, $D$2:$D$689, D67, $E$2:$E$689, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="10"/>
@@ -25005,11 +25010,11 @@
         <v>4763</v>
       </c>
       <c r="M68" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>253</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B68, $C$2:$C$689, C68, $D$2:$D$689, D68, $E$2:$E$689, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25051,11 +25056,11 @@
         <v>56375</v>
       </c>
       <c r="M69" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34175</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B69, $C$2:$C$689, C69, $D$2:$D$689, D69, $E$2:$E$689, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25097,11 +25102,11 @@
         <v>10250</v>
       </c>
       <c r="M70" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B70, $C$2:$C$689, C70, $D$2:$D$689, D70, $E$2:$E$689, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25143,11 +25148,11 @@
         <v>32200</v>
       </c>
       <c r="M71" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B71, $C$2:$C$689, C71, $D$2:$D$689, D71, $E$2:$E$689, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="38" t="s">
@@ -25192,11 +25197,11 @@
         <v>39300</v>
       </c>
       <c r="M72" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18850</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B72, $C$2:$C$689, C72, $D$2:$D$689, D72, $E$2:$E$689, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25238,11 +25243,11 @@
         <v>4640</v>
       </c>
       <c r="M73" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B73, $C$2:$C$689, C73, $D$2:$D$689, D73, $E$2:$E$689, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="38" t="s">
@@ -25288,11 +25293,11 @@
         <v>8220</v>
       </c>
       <c r="M74" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B74, $C$2:$C$689, C74, $D$2:$D$689, D74, $E$2:$E$689, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="38" t="s">
@@ -25338,11 +25343,11 @@
         <v>16832</v>
       </c>
       <c r="M75" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1008</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B75, $C$2:$C$689, C75, $D$2:$D$689, D75, $E$2:$E$689, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25378,7 +25383,7 @@
         <v>117</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B76, $C$2:$C$689, C76, $D$2:$D$689, D76, $E$2:$E$689, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25420,11 +25425,11 @@
         <v>10400</v>
       </c>
       <c r="M77" s="18">
-        <f t="shared" ref="M77:M98" si="1">ABS((D77*E77)-L77)</f>
+        <f t="shared" ref="M77:M98" si="3">ABS((D77*E77)-L77)</f>
         <v>300</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B77, $C$2:$C$689, C77, $D$2:$D$689, D77, $E$2:$E$689, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25466,11 +25471,11 @@
         <v>11660</v>
       </c>
       <c r="M78" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B78, $C$2:$C$689, C78, $D$2:$D$689, D78, $E$2:$E$689, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="38" t="s">
@@ -25515,11 +25520,11 @@
         <v>35200</v>
       </c>
       <c r="M79" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B79, $C$2:$C$689, C79, $D$2:$D$689, D79, $E$2:$E$689, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25561,11 +25566,11 @@
         <v>32900</v>
       </c>
       <c r="M80" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B80, $C$2:$C$689, C80, $D$2:$D$689, D80, $E$2:$E$689, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25607,11 +25612,11 @@
         <v>6127.5</v>
       </c>
       <c r="M81" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>612.5</v>
       </c>
       <c r="N81" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B81, $C$2:$C$689, C81, $D$2:$D$689, D81, $E$2:$E$689, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O81" s="29"/>
@@ -25655,11 +25660,11 @@
         <v>6320</v>
       </c>
       <c r="M82" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="N82" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B82, $C$2:$C$689, C82, $D$2:$D$689, D82, $E$2:$E$689, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="29"/>
@@ -25703,11 +25708,11 @@
         <v>3300</v>
       </c>
       <c r="M83" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B83, $C$2:$C$689, C83, $D$2:$D$689, D83, $E$2:$E$689, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25749,11 +25754,11 @@
         <v>8420</v>
       </c>
       <c r="M84" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B84, $C$2:$C$689, C84, $D$2:$D$689, D84, $E$2:$E$689, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25795,11 +25800,11 @@
         <v>16755</v>
       </c>
       <c r="M85" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B85, $C$2:$C$689, C85, $D$2:$D$689, D85, $E$2:$E$689, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="10"/>
@@ -25843,11 +25848,11 @@
         <v>19730.5</v>
       </c>
       <c r="M86" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N86" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B86, $C$2:$C$689, C86, $D$2:$D$689, D86, $E$2:$E$689, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O86" s="38" t="s">
@@ -25893,11 +25898,11 @@
         <v>19690</v>
       </c>
       <c r="M87" s="27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N87" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B87, $C$2:$C$689, C87, $D$2:$D$689, D87, $E$2:$E$689, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
       <c r="O87" s="38" t="s">
@@ -25943,11 +25948,11 @@
         <v>16580</v>
       </c>
       <c r="M88" s="44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>660</v>
       </c>
       <c r="N88" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B88, $C$2:$C$689, C88, $D$2:$D$689, D88, $E$2:$E$689, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="24"/>
@@ -25994,11 +25999,11 @@
         <v>8870</v>
       </c>
       <c r="M89" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B89, $C$2:$C$689, C89, $D$2:$D$689, D89, $E$2:$E$689, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26040,11 +26045,11 @@
         <v>8320</v>
       </c>
       <c r="M90" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B90, $C$2:$C$689, C90, $D$2:$D$689, D90, $E$2:$E$689, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
@@ -26089,14 +26094,13 @@
         <v>14550</v>
       </c>
       <c r="M91" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B91, $C$2:$C$689, C91, $D$2:$D$689, D91, $E$2:$E$689, E91) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O91" s="58"/>
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="92" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3">
@@ -26136,11 +26140,11 @@
         <v>14130</v>
       </c>
       <c r="M92" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>714</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B92, $C$2:$C$689, C92, $D$2:$D$689, D92, $E$2:$E$689, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26182,11 +26186,11 @@
         <v>15075</v>
       </c>
       <c r="M93" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>645</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B93, $C$2:$C$689, C93, $D$2:$D$689, D93, $E$2:$E$689, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="38" t="s">
@@ -26231,11 +26235,11 @@
         <v>6367.2</v>
       </c>
       <c r="M94" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B94, $C$2:$C$689, C94, $D$2:$D$689, D94, $E$2:$E$689, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="38" t="s">
@@ -26280,11 +26284,11 @@
         <v>4200</v>
       </c>
       <c r="M95" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>290</v>
       </c>
       <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B95, $C$2:$C$689, C95, $D$2:$D$689, D95, $E$2:$E$689, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26326,11 +26330,11 @@
         <v>8400</v>
       </c>
       <c r="M96" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B96, $C$2:$C$689, C96, $D$2:$D$689, D96, $E$2:$E$689, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26372,11 +26376,11 @@
         <v>5450</v>
       </c>
       <c r="M97" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B97, $C$2:$C$689, C97, $D$2:$D$689, D97, $E$2:$E$689, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26418,11 +26422,11 @@
         <v>39300</v>
       </c>
       <c r="M98" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>18350</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B98, $C$2:$C$689, C98, $D$2:$D$689, D98, $E$2:$E$689, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26458,7 +26462,7 @@
         <v>117</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B99, $C$2:$C$689, C99, $D$2:$D$689, D99, $E$2:$E$689, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26500,11 +26504,11 @@
         <v>33200</v>
       </c>
       <c r="M100" s="18">
-        <f t="shared" ref="M100:M110" si="2">ABS((D100*E100)-L100)</f>
+        <f t="shared" ref="M100:M110" si="4">ABS((D100*E100)-L100)</f>
         <v>1200</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B100, $C$2:$C$689, C100, $D$2:$D$689, D100, $E$2:$E$689, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26546,11 +26550,11 @@
         <v>20010</v>
       </c>
       <c r="M101" s="18">
+        <f t="shared" si="4"/>
+        <v>450</v>
+      </c>
+      <c r="N101" t="str">
         <f t="shared" si="2"/>
-        <v>450</v>
-      </c>
-      <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B101, $C$2:$C$689, C101, $D$2:$D$689, D101, $E$2:$E$689, E101) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P101"/>
@@ -26593,11 +26597,11 @@
         <v>2868.2</v>
       </c>
       <c r="M102" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N102" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B102, $C$2:$C$689, C102, $D$2:$D$689, D102, $E$2:$E$689, E102) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26639,11 +26643,11 @@
         <v>8480</v>
       </c>
       <c r="M103" s="26">
+        <f t="shared" si="4"/>
+        <v>280</v>
+      </c>
+      <c r="N103" t="str">
         <f t="shared" si="2"/>
-        <v>280</v>
-      </c>
-      <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B103, $C$2:$C$689, C103, $D$2:$D$689, D103, $E$2:$E$689, E103) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O103" s="38" t="s">
@@ -26690,11 +26694,11 @@
         <v>8870</v>
       </c>
       <c r="M104" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N104" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B104, $C$2:$C$689, C104, $D$2:$D$689, D104, $E$2:$E$689, E104) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O104" s="10"/>
@@ -26738,11 +26742,11 @@
         <v>15300</v>
       </c>
       <c r="M105" s="18">
+        <f t="shared" si="4"/>
+        <v>420</v>
+      </c>
+      <c r="N105" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>420</v>
-      </c>
-      <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B105, $C$2:$C$689, C105, $D$2:$D$689, D105, $E$2:$E$689, E105) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26784,11 +26788,11 @@
         <v>10300</v>
       </c>
       <c r="M106" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N106" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B106, $C$2:$C$689, C106, $D$2:$D$689, D106, $E$2:$E$689, E106) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P106" s="29"/>
@@ -26831,11 +26835,11 @@
         <v>17040</v>
       </c>
       <c r="M107" s="18">
+        <f t="shared" si="4"/>
+        <v>880</v>
+      </c>
+      <c r="N107" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>880</v>
-      </c>
-      <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B107, $C$2:$C$689, C107, $D$2:$D$689, D107, $E$2:$E$689, E107) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O107" s="38" t="s">
@@ -26880,11 +26884,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M108" s="18">
+        <f t="shared" si="4"/>
+        <v>710.99999999999636</v>
+      </c>
+      <c r="N108" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>710.99999999999636</v>
-      </c>
-      <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B108, $C$2:$C$689, C108, $D$2:$D$689, D108, $E$2:$E$689, E108) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P108"/>
@@ -26927,11 +26931,11 @@
         <v>20260</v>
       </c>
       <c r="M109" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N109" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N109" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B109, $C$2:$C$689, C109, $D$2:$D$689, D109, $E$2:$E$689, E109) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O109"/>
@@ -26975,11 +26979,11 @@
         <v>4852</v>
       </c>
       <c r="M110" s="18">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="N110" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B110, $C$2:$C$689, C110, $D$2:$D$689, D110, $E$2:$E$689, E110) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -27013,7 +27017,7 @@
       </c>
       <c r="J111" s="34"/>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B111, $C$2:$C$689, C111, $D$2:$D$689, D111, $E$2:$E$689, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="38" t="s">
@@ -27063,7 +27067,7 @@
         <v>1014.5</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B112, $C$2:$C$689, C112, $D$2:$D$689, D112, $E$2:$E$689, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27099,7 +27103,7 @@
         <v>116</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B113, $C$2:$C$689, C113, $D$2:$D$689, D113, $E$2:$E$689, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27145,7 +27149,7 @@
         <v>654</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B114, $C$2:$C$689, C114, $D$2:$D$689, D114, $E$2:$E$689, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27191,7 +27195,7 @@
         <v>850</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B115, $C$2:$C$689, C115, $D$2:$D$689, D115, $E$2:$E$689, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27228,7 +27232,7 @@
       <c r="L116" s="18"/>
       <c r="M116" s="18"/>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B116, $C$2:$C$689, C116, $D$2:$D$689, D116, $E$2:$E$689, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="10"/>
@@ -27272,11 +27276,11 @@
         <v>4120</v>
       </c>
       <c r="M117" s="27">
-        <f t="shared" ref="M117:M124" si="3">ABS((D117*E117)-L117)</f>
+        <f t="shared" ref="M117:M124" si="5">ABS((D117*E117)-L117)</f>
         <v>270</v>
       </c>
       <c r="N117" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B117, $C$2:$C$689, C117, $D$2:$D$689, D117, $E$2:$E$689, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="39" t="s">
@@ -27322,11 +27326,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M118" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N118" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B118, $C$2:$C$689, C118, $D$2:$D$689, D118, $E$2:$E$689, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="39" t="s">
@@ -27372,11 +27376,11 @@
         <v>17150</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B119, $C$2:$C$689, C119, $D$2:$D$689, D119, $E$2:$E$689, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27418,11 +27422,11 @@
         <v>20070</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>810</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B120, $C$2:$C$689, C120, $D$2:$D$689, D120, $E$2:$E$689, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27465,11 +27469,11 @@
         <v>8970</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B121, $C$2:$C$689, C121, $D$2:$D$689, D121, $E$2:$E$689, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="10"/>
@@ -27513,11 +27517,11 @@
         <v>10410</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B122, $C$2:$C$689, C122, $D$2:$D$689, D122, $E$2:$E$689, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="29"/>
@@ -27560,11 +27564,11 @@
         <v>3400</v>
       </c>
       <c r="M123" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>250</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B123, $C$2:$C$689, C123, $D$2:$D$689, D123, $E$2:$E$689, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27606,11 +27610,11 @@
         <v>8570</v>
       </c>
       <c r="M124" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B124, $C$2:$C$689, C124, $D$2:$D$689, D124, $E$2:$E$689, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="38" t="s">
@@ -27647,7 +27651,7 @@
       </c>
       <c r="J125" s="34"/>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B125, $C$2:$C$689, C125, $D$2:$D$689, D125, $E$2:$E$689, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="24"/>
@@ -27694,7 +27698,7 @@
         <v>300</v>
       </c>
       <c r="N126" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B126, $C$2:$C$689, C126, $D$2:$D$689, D126, $E$2:$E$689, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="10"/>
@@ -27742,7 +27746,7 @@
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B127, $C$2:$C$689, C127, $D$2:$D$689, D127, $E$2:$E$689, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27781,7 +27785,7 @@
         <v>143</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B128, $C$2:$C$689, C128, $D$2:$D$689, D128, $E$2:$E$689, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27823,11 +27827,11 @@
         <v>10510</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" ref="M129:M136" si="4">ABS((D129*E129)-L129)</f>
+        <f t="shared" ref="M129:M136" si="6">ABS((D129*E129)-L129)</f>
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B129, $C$2:$C$689, C129, $D$2:$D$689, D129, $E$2:$E$689, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="10"/>
@@ -27871,11 +27875,11 @@
         <v>5520</v>
       </c>
       <c r="M130" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N130" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B130, $C$2:$C$689, C130, $D$2:$D$689, D130, $E$2:$E$689, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="7">IF(COUNTIFS( $B$2:$B$689, B130, $C$2:$C$689, C130, $D$2:$D$689, D130, $E$2:$E$689, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="38" t="s">
@@ -27920,11 +27924,11 @@
         <v>2657</v>
       </c>
       <c r="M131" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>253</v>
       </c>
       <c r="N131" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B131, $C$2:$C$689, C131, $D$2:$D$689, D131, $E$2:$E$689, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O131" s="38" t="s">
@@ -27969,11 +27973,11 @@
         <v>2554.5</v>
       </c>
       <c r="M132" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>355.5</v>
       </c>
       <c r="N132" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B132, $C$2:$C$689, C132, $D$2:$D$689, D132, $E$2:$E$689, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O132" s="38" t="s">
@@ -28019,11 +28023,11 @@
         <v>9170</v>
       </c>
       <c r="M133" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B133, $C$2:$C$689, C133, $D$2:$D$689, D133, $E$2:$E$689, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="38" t="s">
@@ -28068,11 +28072,11 @@
         <v>7578</v>
       </c>
       <c r="M134" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N134" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B134, $C$2:$C$689, C134, $D$2:$D$689, D134, $E$2:$E$689, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O134" s="10"/>
@@ -28116,11 +28120,11 @@
         <v>7578</v>
       </c>
       <c r="M135" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N135" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B135, $C$2:$C$689, C135, $D$2:$D$689, D135, $E$2:$E$689, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O135" s="10"/>
@@ -28164,11 +28168,11 @@
         <v>4968</v>
       </c>
       <c r="M136" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="N136" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B136, $C$2:$C$689, C136, $D$2:$D$689, D136, $E$2:$E$689, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="29"/>
@@ -28206,7 +28210,7 @@
         <v>116</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B137, $C$2:$C$689, C137, $D$2:$D$689, D137, $E$2:$E$689, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28242,7 +28246,7 @@
         <v>116</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B138, $C$2:$C$689, C138, $D$2:$D$689, D138, $E$2:$E$689, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28288,7 +28292,7 @@
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B139, $C$2:$C$689, C139, $D$2:$D$689, D139, $E$2:$E$689, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28334,7 +28338,7 @@
         <v>376</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B140, $C$2:$C$689, C140, $D$2:$D$689, D140, $E$2:$E$689, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28370,7 +28374,7 @@
         <v>117</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B141, $C$2:$C$689, C141, $D$2:$D$689, D141, $E$2:$E$689, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28416,7 +28420,7 @@
         <v>1400</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B142, $C$2:$C$689, C142, $D$2:$D$689, D142, $E$2:$E$689, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="38" t="s">
@@ -28465,7 +28469,7 @@
         <v>500</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B143, $C$2:$C$689, C143, $D$2:$D$689, D143, $E$2:$E$689, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28499,7 +28503,7 @@
       </c>
       <c r="J144" s="34"/>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B144, $C$2:$C$689, C144, $D$2:$D$689, D144, $E$2:$E$689, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28536,7 +28540,7 @@
       <c r="L145" s="18"/>
       <c r="M145" s="18"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B145, $C$2:$C$689, C145, $D$2:$D$689, D145, $E$2:$E$689, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="10"/>
@@ -28584,7 +28588,7 @@
         <v>500</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B146, $C$2:$C$689, C146, $D$2:$D$689, D146, $E$2:$E$689, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="39" t="s">
@@ -28634,7 +28638,7 @@
         <v>527.5</v>
       </c>
       <c r="N147" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B147, $C$2:$C$689, C147, $D$2:$D$689, D147, $E$2:$E$689, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="29"/>
@@ -28677,7 +28681,7 @@
       <c r="L148" s="27"/>
       <c r="M148" s="27"/>
       <c r="N148" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B148, $C$2:$C$689, C148, $D$2:$D$689, D148, $E$2:$E$689, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="29"/>
@@ -28725,7 +28729,7 @@
         <v>395</v>
       </c>
       <c r="N149" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B149, $C$2:$C$689, C149, $D$2:$D$689, D149, $E$2:$E$689, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="38" t="s">
@@ -28775,7 +28779,7 @@
         <v>250</v>
       </c>
       <c r="N150" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B150, $C$2:$C$689, C150, $D$2:$D$689, D150, $E$2:$E$689, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O150" s="38" t="s">
@@ -28825,7 +28829,7 @@
         <v>300</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B151, $C$2:$C$689, C151, $D$2:$D$689, D151, $E$2:$E$689, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28859,7 +28863,7 @@
       </c>
       <c r="J152" s="34"/>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B152, $C$2:$C$689, C152, $D$2:$D$689, D152, $E$2:$E$689, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="29"/>
@@ -28906,7 +28910,7 @@
         <v>320</v>
       </c>
       <c r="N153" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B153, $C$2:$C$689, C153, $D$2:$D$689, D153, $E$2:$E$689, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="29"/>
@@ -28954,7 +28958,7 @@
         <v>235</v>
       </c>
       <c r="N154" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B154, $C$2:$C$689, C154, $D$2:$D$689, D154, $E$2:$E$689, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="29"/>
@@ -29002,7 +29006,7 @@
         <v>300</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B155, $C$2:$C$689, C155, $D$2:$D$689, D155, $E$2:$E$689, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O155"/>
@@ -29049,7 +29053,7 @@
         <v>500</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B156, $C$2:$C$689, C156, $D$2:$D$689, D156, $E$2:$E$689, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29088,7 +29092,7 @@
       <c r="L157" s="18"/>
       <c r="M157" s="18"/>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B157, $C$2:$C$689, C157, $D$2:$D$689, D157, $E$2:$E$689, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O157" s="10"/>
@@ -29136,7 +29140,7 @@
         <v>1700</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B158, $C$2:$C$689, C158, $D$2:$D$689, D158, $E$2:$E$689, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O158" s="29"/>
@@ -29183,7 +29187,7 @@
         <v>650</v>
       </c>
       <c r="N159" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B159, $C$2:$C$689, C159, $D$2:$D$689, D159, $E$2:$E$689, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29217,7 +29221,7 @@
       </c>
       <c r="J160" s="34"/>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B160, $C$2:$C$689, C160, $D$2:$D$689, D160, $E$2:$E$689, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P160" s="29"/>
@@ -29264,7 +29268,7 @@
         <v>501</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B161, $C$2:$C$689, C161, $D$2:$D$689, D161, $E$2:$E$689, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="38" t="s">
@@ -29306,7 +29310,7 @@
       <c r="L162" s="18"/>
       <c r="M162" s="18"/>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B162, $C$2:$C$689, C162, $D$2:$D$689, D162, $E$2:$E$689, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O162" s="10"/>
@@ -29354,7 +29358,7 @@
         <v>250</v>
       </c>
       <c r="N163" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B163, $C$2:$C$689, C163, $D$2:$D$689, D163, $E$2:$E$689, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29400,7 +29404,7 @@
         <v>275</v>
       </c>
       <c r="N164" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B164, $C$2:$C$689, C164, $D$2:$D$689, D164, $E$2:$E$689, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29446,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="N165" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B165, $C$2:$C$689, C165, $D$2:$D$689, D165, $E$2:$E$689, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29480,7 +29484,7 @@
       </c>
       <c r="J166" s="34"/>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B166, $C$2:$C$689, C166, $D$2:$D$689, D166, $E$2:$E$689, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29519,7 +29523,7 @@
       <c r="L167" s="17"/>
       <c r="M167" s="17"/>
       <c r="N167" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B167, $C$2:$C$689, C167, $D$2:$D$689, D167, $E$2:$E$689, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29565,7 +29569,7 @@
         <v>140</v>
       </c>
       <c r="N168" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B168, $C$2:$C$689, C168, $D$2:$D$689, D168, $E$2:$E$689, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="P168" s="29"/>
@@ -29612,7 +29616,7 @@
         <v>300</v>
       </c>
       <c r="N169" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B169, $C$2:$C$689, C169, $D$2:$D$689, D169, $E$2:$E$689, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29658,7 +29662,7 @@
         <v>300</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B170, $C$2:$C$689, C170, $D$2:$D$689, D170, $E$2:$E$689, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P170" s="19"/>
@@ -29693,7 +29697,7 @@
       </c>
       <c r="J171" s="34"/>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B171, $C$2:$C$689, C171, $D$2:$D$689, D171, $E$2:$E$689, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29739,7 +29743,7 @@
         <v>650</v>
       </c>
       <c r="N172" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B172, $C$2:$C$689, C172, $D$2:$D$689, D172, $E$2:$E$689, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="29"/>
@@ -29787,7 +29791,7 @@
         <v>934</v>
       </c>
       <c r="N173" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B173, $C$2:$C$689, C173, $D$2:$D$689, D173, $E$2:$E$689, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="29"/>
@@ -29828,7 +29832,7 @@
       <c r="L174" s="44"/>
       <c r="M174" s="44"/>
       <c r="N174" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B174, $C$2:$C$689, C174, $D$2:$D$689, D174, $E$2:$E$689, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="24"/>
@@ -29868,7 +29872,7 @@
         <v>117</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B175, $C$2:$C$689, C175, $D$2:$D$689, D175, $E$2:$E$689, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29914,7 +29918,7 @@
         <v>800</v>
       </c>
       <c r="N176" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B176, $C$2:$C$689, C176, $D$2:$D$689, D176, $E$2:$E$689, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29950,7 +29954,7 @@
         <v>117</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B177, $C$2:$C$689, C177, $D$2:$D$689, D177, $E$2:$E$689, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="38" t="s">
@@ -29999,7 +30003,7 @@
         <v>260</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B178, $C$2:$C$689, C178, $D$2:$D$689, D178, $E$2:$E$689, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30045,7 +30049,7 @@
         <v>500</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B179, $C$2:$C$689, C179, $D$2:$D$689, D179, $E$2:$E$689, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30081,7 +30085,7 @@
         <v>116</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B180, $C$2:$C$689, C180, $D$2:$D$689, D180, $E$2:$E$689, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30127,7 +30131,7 @@
         <v>300</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B181, $C$2:$C$689, C181, $D$2:$D$689, D181, $E$2:$E$689, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="38" t="s">
@@ -30164,7 +30168,7 @@
       </c>
       <c r="J182" s="34"/>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B182, $C$2:$C$689, C182, $D$2:$D$689, D182, $E$2:$E$689, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30210,7 +30214,7 @@
         <v>300</v>
       </c>
       <c r="N183" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B183, $C$2:$C$689, C183, $D$2:$D$689, D183, $E$2:$E$689, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="29"/>
@@ -30258,7 +30262,7 @@
         <v>188</v>
       </c>
       <c r="N184" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B184, $C$2:$C$689, C184, $D$2:$D$689, D184, $E$2:$E$689, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="29"/>
@@ -30294,7 +30298,7 @@
       </c>
       <c r="J185" s="34"/>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B185, $C$2:$C$689, C185, $D$2:$D$689, D185, $E$2:$E$689, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30330,7 +30334,7 @@
         <v>117</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B186, $C$2:$C$689, C186, $D$2:$D$689, D186, $E$2:$E$689, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30376,7 +30380,7 @@
         <v>646</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B187, $C$2:$C$689, C187, $D$2:$D$689, D187, $E$2:$E$689, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="38" t="s">
@@ -30415,7 +30419,7 @@
         <v>117</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B188, $C$2:$C$689, C188, $D$2:$D$689, D188, $E$2:$E$689, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30451,7 +30455,7 @@
         <v>117</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B189, $C$2:$C$689, C189, $D$2:$D$689, D189, $E$2:$E$689, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30490,7 +30494,7 @@
       <c r="L190" s="17"/>
       <c r="M190" s="17"/>
       <c r="N190" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B190, $C$2:$C$689, C190, $D$2:$D$689, D190, $E$2:$E$689, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="10"/>
@@ -30538,7 +30542,7 @@
         <v>650</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B191, $C$2:$C$689, C191, $D$2:$D$689, D191, $E$2:$E$689, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="29"/>
@@ -30573,7 +30577,7 @@
       </c>
       <c r="J192" s="34"/>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B192, $C$2:$C$689, C192, $D$2:$D$689, D192, $E$2:$E$689, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30619,7 +30623,7 @@
         <v>290</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B193, $C$2:$C$689, C193, $D$2:$D$689, D193, $E$2:$E$689, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30665,7 +30669,7 @@
         <v>1000</v>
       </c>
       <c r="N194" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B194, $C$2:$C$689, C194, $D$2:$D$689, D194, $E$2:$E$689, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="8">IF(COUNTIFS( $B$2:$B$689, B194, $C$2:$C$689, C194, $D$2:$D$689, D194, $E$2:$E$689, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P194" s="29"/>
@@ -30712,7 +30716,7 @@
         <v>450</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B195, $C$2:$C$689, C195, $D$2:$D$689, D195, $E$2:$E$689, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30758,7 +30762,7 @@
         <v>300</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B196, $C$2:$C$689, C196, $D$2:$D$689, D196, $E$2:$E$689, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30794,7 +30798,7 @@
         <v>116</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B197, $C$2:$C$689, C197, $D$2:$D$689, D197, $E$2:$E$689, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30830,7 +30834,7 @@
         <v>54</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B198, $C$2:$C$689, C198, $D$2:$D$689, D198, $E$2:$E$689, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30866,7 +30870,7 @@
         <v>116</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B199, $C$2:$C$689, C199, $D$2:$D$689, D199, $E$2:$E$689, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30912,7 +30916,7 @@
         <v>300</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B200, $C$2:$C$689, C200, $D$2:$D$689, D200, $E$2:$E$689, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30946,7 +30950,7 @@
       </c>
       <c r="J201" s="34"/>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B201, $C$2:$C$689, C201, $D$2:$D$689, D201, $E$2:$E$689, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30992,7 +30996,7 @@
         <v>275</v>
       </c>
       <c r="N202" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B202, $C$2:$C$689, C202, $D$2:$D$689, D202, $E$2:$E$689, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31026,7 +31030,7 @@
       </c>
       <c r="J203" s="34"/>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B203, $C$2:$C$689, C203, $D$2:$D$689, D203, $E$2:$E$689, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31072,7 +31076,7 @@
         <v>800</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B204, $C$2:$C$689, C204, $D$2:$D$689, D204, $E$2:$E$689, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="38" t="s">
@@ -31121,7 +31125,7 @@
         <v>360</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B205, $C$2:$C$689, C205, $D$2:$D$689, D205, $E$2:$E$689, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31167,7 +31171,7 @@
         <v>940</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B206, $C$2:$C$689, C206, $D$2:$D$689, D206, $E$2:$E$689, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31213,7 +31217,7 @@
         <v>300</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B207, $C$2:$C$689, C207, $D$2:$D$689, D207, $E$2:$E$689, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P207" s="25"/>
@@ -31248,7 +31252,7 @@
       </c>
       <c r="J208" s="34"/>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B208, $C$2:$C$689, C208, $D$2:$D$689, D208, $E$2:$E$689, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31284,7 +31288,7 @@
         <v>117</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B209, $C$2:$C$689, C209, $D$2:$D$689, D209, $E$2:$E$689, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O209" s="29"/>
@@ -31321,7 +31325,7 @@
         <v>54</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B210, $C$2:$C$689, C210, $D$2:$D$689, D210, $E$2:$E$689, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31355,7 +31359,7 @@
       </c>
       <c r="J211" s="34"/>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B211, $C$2:$C$689, C211, $D$2:$D$689, D211, $E$2:$E$689, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31391,7 +31395,7 @@
         <v>117</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B212, $C$2:$C$689, C212, $D$2:$D$689, D212, $E$2:$E$689, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="29"/>
@@ -31426,7 +31430,7 @@
       </c>
       <c r="J213" s="34"/>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B213, $C$2:$C$689, C213, $D$2:$D$689, D213, $E$2:$E$689, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31460,7 +31464,7 @@
       </c>
       <c r="J214" s="34"/>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B214, $C$2:$C$689, C214, $D$2:$D$689, D214, $E$2:$E$689, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31506,7 +31510,7 @@
         <v>150</v>
       </c>
       <c r="N215" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B215, $C$2:$C$689, C215, $D$2:$D$689, D215, $E$2:$E$689, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31552,7 +31556,7 @@
         <v>250</v>
       </c>
       <c r="N216" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B216, $C$2:$C$689, C216, $D$2:$D$689, D216, $E$2:$E$689, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31588,7 +31592,7 @@
         <v>116</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B217, $C$2:$C$689, C217, $D$2:$D$689, D217, $E$2:$E$689, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31634,7 +31638,7 @@
         <v>250</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B218, $C$2:$C$689, C218, $D$2:$D$689, D218, $E$2:$E$689, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31680,7 +31684,7 @@
         <v>300</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B219, $C$2:$C$689, C219, $D$2:$D$689, D219, $E$2:$E$689, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31726,7 +31730,7 @@
         <v>816</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B220, $C$2:$C$689, C220, $D$2:$D$689, D220, $E$2:$E$689, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31772,7 +31776,7 @@
         <v>650</v>
       </c>
       <c r="N221" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B221, $C$2:$C$689, C221, $D$2:$D$689, D221, $E$2:$E$689, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P221" s="29"/>
@@ -31807,7 +31811,7 @@
       </c>
       <c r="J222" s="34"/>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B222, $C$2:$C$689, C222, $D$2:$D$689, D222, $E$2:$E$689, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31843,7 +31847,7 @@
         <v>116</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B223, $C$2:$C$689, C223, $D$2:$D$689, D223, $E$2:$E$689, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31889,7 +31893,7 @@
         <v>450</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B224, $C$2:$C$689, C224, $D$2:$D$689, D224, $E$2:$E$689, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31925,7 +31929,7 @@
         <v>117</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B225, $C$2:$C$689, C225, $D$2:$D$689, D225, $E$2:$E$689, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31971,7 +31975,7 @@
         <v>268</v>
       </c>
       <c r="N226" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B226, $C$2:$C$689, C226, $D$2:$D$689, D226, $E$2:$E$689, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32017,7 +32021,7 @@
         <v>48320</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B227, $C$2:$C$689, C227, $D$2:$D$689, D227, $E$2:$E$689, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="38" t="s">
@@ -32066,7 +32070,7 @@
         <v>250</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B228, $C$2:$C$689, C228, $D$2:$D$689, D228, $E$2:$E$689, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="10"/>
@@ -32106,7 +32110,7 @@
       <c r="L229" s="18"/>
       <c r="M229" s="18"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B229, $C$2:$C$689, C229, $D$2:$D$689, D229, $E$2:$E$689, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="10"/>
@@ -32153,7 +32157,7 @@
         <v>400</v>
       </c>
       <c r="N230" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B230, $C$2:$C$689, C230, $D$2:$D$689, D230, $E$2:$E$689, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32199,7 +32203,7 @@
         <v>320</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B231, $C$2:$C$689, C231, $D$2:$D$689, D231, $E$2:$E$689, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32245,7 +32249,7 @@
         <v>448</v>
       </c>
       <c r="N232" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B232, $C$2:$C$689, C232, $D$2:$D$689, D232, $E$2:$E$689, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32284,7 +32288,7 @@
         <v>144</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B233, $C$2:$C$689, C233, $D$2:$D$689, D233, $E$2:$E$689, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32330,7 +32334,7 @@
         <v>300</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B234, $C$2:$C$689, C234, $D$2:$D$689, D234, $E$2:$E$689, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32376,7 +32380,7 @@
         <v>651</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B235, $C$2:$C$689, C235, $D$2:$D$689, D235, $E$2:$E$689, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32422,7 +32426,7 @@
         <v>300</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B236, $C$2:$C$689, C236, $D$2:$D$689, D236, $E$2:$E$689, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32458,7 +32462,7 @@
         <v>116</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B237, $C$2:$C$689, C237, $D$2:$D$689, D237, $E$2:$E$689, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32504,7 +32508,7 @@
         <v>650</v>
       </c>
       <c r="N238" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B238, $C$2:$C$689, C238, $D$2:$D$689, D238, $E$2:$E$689, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P238" s="29"/>
@@ -32539,7 +32543,7 @@
       </c>
       <c r="J239" s="34"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B239, $C$2:$C$689, C239, $D$2:$D$689, D239, $E$2:$E$689, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32585,7 +32589,7 @@
         <v>235</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B240, $C$2:$C$689, C240, $D$2:$D$689, D240, $E$2:$E$689, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32624,7 +32628,7 @@
       <c r="L241" s="18"/>
       <c r="M241" s="18"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B241, $C$2:$C$689, C241, $D$2:$D$689, D241, $E$2:$E$689, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="10"/>
@@ -32662,7 +32666,7 @@
         <v>116</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B242, $C$2:$C$689, C242, $D$2:$D$689, D242, $E$2:$E$689, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32708,7 +32712,7 @@
         <v>480</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B243, $C$2:$C$689, C243, $D$2:$D$689, D243, $E$2:$E$689, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32742,7 +32746,7 @@
       </c>
       <c r="J244" s="34"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B244, $C$2:$C$689, C244, $D$2:$D$689, D244, $E$2:$E$689, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32779,7 +32783,7 @@
       <c r="L245" s="18"/>
       <c r="M245" s="18"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B245, $C$2:$C$689, C245, $D$2:$D$689, D245, $E$2:$E$689, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -32827,7 +32831,7 @@
         <v>47900</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B246, $C$2:$C$689, C246, $D$2:$D$689, D246, $E$2:$E$689, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="38" t="s">
@@ -32876,7 +32880,7 @@
         <v>370</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B247, $C$2:$C$689, C247, $D$2:$D$689, D247, $E$2:$E$689, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P247" s="29"/>
@@ -32923,7 +32927,7 @@
         <v>250</v>
       </c>
       <c r="N248" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B248, $C$2:$C$689, C248, $D$2:$D$689, D248, $E$2:$E$689, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32969,7 +32973,7 @@
         <v>650</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B249, $C$2:$C$689, C249, $D$2:$D$689, D249, $E$2:$E$689, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="38" t="s">
@@ -33018,7 +33022,7 @@
         <v>495</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B250, $C$2:$C$689, C250, $D$2:$D$689, D250, $E$2:$E$689, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="38" t="s">
@@ -33059,7 +33063,7 @@
       <c r="L251" s="18"/>
       <c r="M251" s="18"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B251, $C$2:$C$689, C251, $D$2:$D$689, D251, $E$2:$E$689, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="10"/>
@@ -33097,7 +33101,7 @@
         <v>117</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B252, $C$2:$C$689, C252, $D$2:$D$689, D252, $E$2:$E$689, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="29"/>
@@ -33144,7 +33148,7 @@
         <v>300</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B253, $C$2:$C$689, C253, $D$2:$D$689, D253, $E$2:$E$689, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33183,7 +33187,7 @@
       <c r="L254" s="18"/>
       <c r="M254" s="18"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B254, $C$2:$C$689, C254, $D$2:$D$689, D254, $E$2:$E$689, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="10"/>
@@ -33231,7 +33235,7 @@
         <v>1800</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B255, $C$2:$C$689, C255, $D$2:$D$689, D255, $E$2:$E$689, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33277,7 +33281,7 @@
         <v>300</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B256, $C$2:$C$689, C256, $D$2:$D$689, D256, $E$2:$E$689, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="38" t="s">
@@ -33320,7 +33324,7 @@
       <c r="L257" s="18"/>
       <c r="M257" s="18"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B257, $C$2:$C$689, C257, $D$2:$D$689, D257, $E$2:$E$689, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="10"/>
@@ -33361,7 +33365,7 @@
       <c r="L258" s="18"/>
       <c r="M258" s="18"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B258, $C$2:$C$689, C258, $D$2:$D$689, D258, $E$2:$E$689, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N301" si="9">IF(COUNTIFS( $B$2:$B$689, B258, $C$2:$C$689, C258, $D$2:$D$689, D258, $E$2:$E$689, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="10"/>
@@ -33397,7 +33401,7 @@
       </c>
       <c r="J259" s="34"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B259, $C$2:$C$689, C259, $D$2:$D$689, D259, $E$2:$E$689, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33431,7 +33435,7 @@
       </c>
       <c r="J260" s="34"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B260, $C$2:$C$689, C260, $D$2:$D$689, D260, $E$2:$E$689, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="29"/>
@@ -33478,7 +33482,7 @@
         <v>500</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B261, $C$2:$C$689, C261, $D$2:$D$689, D261, $E$2:$E$689, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="38" t="s">
@@ -33517,7 +33521,7 @@
         <v>116</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B262, $C$2:$C$689, C262, $D$2:$D$689, D262, $E$2:$E$689, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33553,7 +33557,7 @@
         <v>116</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B263, $C$2:$C$689, C263, $D$2:$D$689, D263, $E$2:$E$689, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33599,7 +33603,7 @@
         <v>650</v>
       </c>
       <c r="N264" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B264, $C$2:$C$689, C264, $D$2:$D$689, D264, $E$2:$E$689, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O264"/>
@@ -33637,7 +33641,7 @@
         <v>116</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B265, $C$2:$C$689, C265, $D$2:$D$689, D265, $E$2:$E$689, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33671,7 +33675,7 @@
       </c>
       <c r="J266" s="34"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B266, $C$2:$C$689, C266, $D$2:$D$689, D266, $E$2:$E$689, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="29"/>
@@ -33718,7 +33722,7 @@
         <v>300</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B267, $C$2:$C$689, C267, $D$2:$D$689, D267, $E$2:$E$689, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33764,7 +33768,7 @@
         <v>47480</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B268, $C$2:$C$689, C268, $D$2:$D$689, D268, $E$2:$E$689, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33810,7 +33814,7 @@
         <v>340</v>
       </c>
       <c r="N269" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B269, $C$2:$C$689, C269, $D$2:$D$689, D269, $E$2:$E$689, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33856,7 +33860,7 @@
         <v>260</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B270, $C$2:$C$689, C270, $D$2:$D$689, D270, $E$2:$E$689, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33892,7 +33896,7 @@
         <v>117</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B271, $C$2:$C$689, C271, $D$2:$D$689, D271, $E$2:$E$689, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33938,7 +33942,7 @@
         <v>300</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B272, $C$2:$C$689, C272, $D$2:$D$689, D272, $E$2:$E$689, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33974,7 +33978,7 @@
         <v>117</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B273, $C$2:$C$689, C273, $D$2:$D$689, D273, $E$2:$E$689, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34020,7 +34024,7 @@
         <v>300</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B274, $C$2:$C$689, C274, $D$2:$D$689, D274, $E$2:$E$689, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="10"/>
@@ -34063,7 +34067,7 @@
       <c r="L275" s="17"/>
       <c r="M275" s="17"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B275, $C$2:$C$689, C275, $D$2:$D$689, D275, $E$2:$E$689, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="10"/>
@@ -34101,7 +34105,7 @@
         <v>116</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B276, $C$2:$C$689, C276, $D$2:$D$689, D276, $E$2:$E$689, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34147,7 +34151,7 @@
         <v>285</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B277, $C$2:$C$689, C277, $D$2:$D$689, D277, $E$2:$E$689, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34193,7 +34197,7 @@
         <v>726</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B278, $C$2:$C$689, C278, $D$2:$D$689, D278, $E$2:$E$689, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34239,7 +34243,7 @@
         <v>300</v>
       </c>
       <c r="N279" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B279, $C$2:$C$689, C279, $D$2:$D$689, D279, $E$2:$E$689, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34275,7 +34279,7 @@
         <v>152</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B280, $C$2:$C$689, C280, $D$2:$D$689, D280, $E$2:$E$689, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34311,7 +34315,7 @@
         <v>117</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B281, $C$2:$C$689, C281, $D$2:$D$689, D281, $E$2:$E$689, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34357,7 +34361,7 @@
         <v>275</v>
       </c>
       <c r="N282" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B282, $C$2:$C$689, C282, $D$2:$D$689, D282, $E$2:$E$689, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34393,7 +34397,7 @@
         <v>116</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B283, $C$2:$C$689, C283, $D$2:$D$689, D283, $E$2:$E$689, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34427,7 +34431,7 @@
       </c>
       <c r="J284" s="34"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B284, $C$2:$C$689, C284, $D$2:$D$689, D284, $E$2:$E$689, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P284" s="29"/>
@@ -34462,7 +34466,7 @@
       </c>
       <c r="J285" s="34"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B285, $C$2:$C$689, C285, $D$2:$D$689, D285, $E$2:$E$689, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P285" s="29"/>
@@ -34509,7 +34513,7 @@
         <v>250</v>
       </c>
       <c r="N286" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B286, $C$2:$C$689, C286, $D$2:$D$689, D286, $E$2:$E$689, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P286" s="29"/>
@@ -34544,7 +34548,7 @@
       </c>
       <c r="J287" s="34"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B287, $C$2:$C$689, C287, $D$2:$D$689, D287, $E$2:$E$689, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34578,7 +34582,7 @@
       </c>
       <c r="J288" s="34"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B288, $C$2:$C$689, C288, $D$2:$D$689, D288, $E$2:$E$689, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34624,7 +34628,7 @@
         <v>250</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B289, $C$2:$C$689, C289, $D$2:$D$689, D289, $E$2:$E$689, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34658,7 +34662,7 @@
       </c>
       <c r="J290" s="34"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B290, $C$2:$C$689, C290, $D$2:$D$689, D290, $E$2:$E$689, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34692,7 +34696,7 @@
       </c>
       <c r="J291" s="34"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B291, $C$2:$C$689, C291, $D$2:$D$689, D291, $E$2:$E$689, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34728,7 +34732,7 @@
         <v>54</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B292, $C$2:$C$689, C292, $D$2:$D$689, D292, $E$2:$E$689, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34774,7 +34778,7 @@
         <v>300</v>
       </c>
       <c r="N293" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B293, $C$2:$C$689, C293, $D$2:$D$689, D293, $E$2:$E$689, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34810,7 +34814,7 @@
         <v>117</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B294, $C$2:$C$689, C294, $D$2:$D$689, D294, $E$2:$E$689, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34846,7 +34850,7 @@
         <v>117</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B295, $C$2:$C$689, C295, $D$2:$D$689, D295, $E$2:$E$689, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34882,7 +34886,7 @@
         <v>117</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B296, $C$2:$C$689, C296, $D$2:$D$689, D296, $E$2:$E$689, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34928,7 +34932,7 @@
         <v>250</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B297, $C$2:$C$689, C297, $D$2:$D$689, D297, $E$2:$E$689, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O297" s="10"/>
@@ -34964,7 +34968,7 @@
       </c>
       <c r="J298" s="34"/>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B298, $C$2:$C$689, C298, $D$2:$D$689, D298, $E$2:$E$689, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35003,7 +35007,7 @@
       <c r="L299" s="27"/>
       <c r="M299" s="27"/>
       <c r="N299" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B299, $C$2:$C$689, C299, $D$2:$D$689, D299, $E$2:$E$689, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35042,7 +35046,7 @@
       <c r="L300" s="27"/>
       <c r="M300" s="27"/>
       <c r="N300" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B300, $C$2:$C$689, C300, $D$2:$D$689, D300, $E$2:$E$689, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O300" s="29"/>
@@ -35080,7 +35084,7 @@
         <v>116</v>
       </c>
       <c r="N301" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$689, B301, $C$2:$C$689, C301, $D$2:$D$689, D301, $E$2:$E$689, E301) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_5oct26_Mon.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_5oct26_Mon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F6ACE6-B348-49F8-B145-2A059727FCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9400A34-7E18-48EC-B81C-962B072C198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1646,7 +1646,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P981"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1708,7 +1707,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46281.416666666664</v>
       </c>
@@ -1756,7 +1755,7 @@
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
     </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>61</v>
       </c>
@@ -1795,7 +1794,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46281.416666666664</v>
       </c>
@@ -1843,7 +1842,7 @@
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>61</v>
       </c>
@@ -1857,7 +1856,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="4">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="F5" s="4">
         <v>-24.731182799999999</v>
@@ -1882,7 +1881,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>61</v>
       </c>
@@ -1921,7 +1920,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>61</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>61</v>
       </c>
@@ -1995,7 +1994,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="9" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -2034,7 +2033,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="10" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>61</v>
       </c>
@@ -2073,7 +2072,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>61</v>
       </c>
@@ -2110,7 +2109,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="12" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>61</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>61</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>46031.4375</v>
       </c>
@@ -2227,7 +2226,7 @@
       </c>
       <c r="P14" s="19"/>
     </row>
-    <row r="15" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="49">
         <v>46289.375</v>
       </c>
@@ -2273,7 +2272,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>61</v>
       </c>
@@ -2312,7 +2311,7 @@
       <c r="O16"/>
       <c r="P16"/>
     </row>
-    <row r="17" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2351,7 +2350,7 @@
       <c r="O17"/>
       <c r="P17"/>
     </row>
-    <row r="18" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
         <v>61</v>
       </c>
@@ -2392,7 +2391,7 @@
       <c r="O18"/>
       <c r="P18"/>
     </row>
-    <row r="19" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
         <v>61</v>
       </c>
@@ -2431,7 +2430,7 @@
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="49">
         <v>46295.375</v>
       </c>
@@ -2479,7 +2478,7 @@
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
     </row>
-    <row r="21" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6" t="s">
         <v>61</v>
       </c>
@@ -2518,7 +2517,7 @@
       <c r="O21"/>
       <c r="P21"/>
     </row>
-    <row r="22" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="49">
         <v>46300.375694444447</v>
       </c>
@@ -2564,7 +2563,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>61</v>
       </c>
@@ -2605,7 +2604,7 @@
       <c r="O23"/>
       <c r="P23"/>
     </row>
-    <row r="24" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>61</v>
       </c>
@@ -2644,7 +2643,7 @@
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>61</v>
       </c>
@@ -2683,7 +2682,7 @@
       <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
         <v>61</v>
       </c>
@@ -2722,7 +2721,7 @@
       <c r="O26"/>
       <c r="P26"/>
     </row>
-    <row r="27" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>61</v>
       </c>
@@ -2761,7 +2760,7 @@
       <c r="O27"/>
       <c r="P27"/>
     </row>
-    <row r="28" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>46300.375694444447</v>
       </c>
@@ -2808,7 +2807,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <v>46254.375</v>
       </c>
@@ -2851,7 +2850,7 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2891,7 +2890,7 @@
       </c>
       <c r="P30"/>
     </row>
-    <row r="31" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
         <v>61</v>
       </c>
@@ -2930,7 +2929,7 @@
       <c r="O31"/>
       <c r="P31"/>
     </row>
-    <row r="32" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
         <v>61</v>
       </c>
@@ -2970,7 +2969,7 @@
       </c>
       <c r="P32" s="25"/>
     </row>
-    <row r="33" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
         <v>46286.375</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="34" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
         <v>61</v>
       </c>
@@ -3058,7 +3057,7 @@
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <v>46121.375</v>
       </c>
@@ -3107,7 +3106,7 @@
       <c r="O35"/>
       <c r="P35"/>
     </row>
-    <row r="36" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>61</v>
       </c>
@@ -3146,7 +3145,7 @@
       <c r="O36"/>
       <c r="P36"/>
     </row>
-    <row r="37" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>61</v>
       </c>
@@ -3184,7 +3183,7 @@
       </c>
       <c r="O37"/>
     </row>
-    <row r="38" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -3232,7 +3231,7 @@
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="39" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -3273,7 +3272,7 @@
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <v>46261.375</v>
       </c>
@@ -3320,7 +3319,7 @@
       </c>
       <c r="P40" s="24"/>
     </row>
-    <row r="41" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
         <v>46283.375</v>
       </c>
@@ -3366,7 +3365,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="42" spans="1:16" s="24" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" s="24" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="6" t="s">
         <v>61</v>
       </c>
@@ -3407,7 +3406,7 @@
       <c r="O42"/>
       <c r="P42" s="10"/>
     </row>
-    <row r="43" spans="1:16" s="29" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" s="29" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="6" t="s">
         <v>61</v>
       </c>
@@ -3448,7 +3447,7 @@
       <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
         <v>61</v>
       </c>
@@ -3489,7 +3488,7 @@
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="6" t="s">
         <v>61</v>
       </c>
@@ -3528,7 +3527,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="46" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>61</v>
       </c>
@@ -3569,7 +3568,7 @@
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
     </row>
-    <row r="47" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <v>46252.6875</v>
       </c>
@@ -3610,7 +3609,7 @@
       <c r="O47" s="10"/>
       <c r="P47" s="10"/>
     </row>
-    <row r="48" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="6" t="s">
         <v>61</v>
       </c>
@@ -3649,7 +3648,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="49" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="6" t="s">
         <v>61</v>
       </c>
@@ -3687,7 +3686,7 @@
       </c>
       <c r="P49" s="10"/>
     </row>
-    <row r="50" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
         <v>46268.385416666664</v>
       </c>
@@ -3735,7 +3734,7 @@
       <c r="O50" s="10"/>
       <c r="P50" s="10"/>
     </row>
-    <row r="51" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="6" t="s">
         <v>61</v>
       </c>
@@ -3774,7 +3773,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <v>46260.375</v>
       </c>
@@ -3822,7 +3821,7 @@
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
     </row>
-    <row r="53" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="6" t="s">
         <v>61</v>
       </c>
@@ -3859,7 +3858,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="54" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="6" t="s">
         <v>61</v>
       </c>
@@ -3900,7 +3899,7 @@
       <c r="O54"/>
       <c r="P54"/>
     </row>
-    <row r="55" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="49">
         <v>46293.375</v>
       </c>
@@ -3993,7 +3992,7 @@
       </c>
       <c r="P56"/>
     </row>
-    <row r="57" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="6" t="s">
         <v>61</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="59" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6" t="s">
         <v>61</v>
       </c>
@@ -4117,7 +4116,7 @@
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
     </row>
-    <row r="60" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3">
         <v>46252.6875</v>
       </c>
@@ -4204,7 +4203,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="62" spans="1:16" s="24" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" s="24" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="6" t="s">
         <v>61</v>
       </c>
@@ -4384,7 +4383,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3">
         <v>46261.375</v>
       </c>
@@ -4444,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="5">
-        <v>20200</v>
+        <v>20020</v>
       </c>
       <c r="F67" s="4">
         <v>4.0486247039999999</v>
@@ -4469,7 +4468,7 @@
       </c>
       <c r="M67" s="18">
         <f>ABS((D67*E67)-L67)</f>
-        <v>650</v>
+        <v>470</v>
       </c>
       <c r="N67" s="10" t="str">
         <f t="shared" si="1"/>
@@ -4478,7 +4477,7 @@
       <c r="O67" s="10"/>
       <c r="P67" s="10"/>
     </row>
-    <row r="68" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>61</v>
       </c>
@@ -4609,7 +4608,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
         <v>46268.375</v>
       </c>
@@ -4658,7 +4657,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4699,7 +4698,7 @@
       <c r="O72"/>
       <c r="P72"/>
     </row>
-    <row r="73" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>46281.376388888886</v>
       </c>
@@ -4749,7 +4748,7 @@
       </c>
       <c r="P73" s="10"/>
     </row>
-    <row r="74" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>46267.375</v>
       </c>
@@ -4799,7 +4798,7 @@
       </c>
       <c r="P74" s="10"/>
     </row>
-    <row r="75" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -4838,7 +4837,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
         <v>46275.457638888889</v>
       </c>
@@ -4920,7 +4919,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
         <v>46274.375</v>
       </c>
@@ -5062,7 +5061,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3">
         <v>46287.375</v>
       </c>
@@ -5285,7 +5284,7 @@
       <c r="O85" s="10"/>
       <c r="P85" s="10"/>
     </row>
-    <row r="86" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="40">
         <v>46273.375</v>
       </c>
@@ -5335,7 +5334,7 @@
       </c>
       <c r="P86" s="29"/>
     </row>
-    <row r="87" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30">
         <v>46274.375</v>
       </c>
@@ -5445,7 +5444,7 @@
         <v>5</v>
       </c>
       <c r="E89" s="5">
-        <v>1794</v>
+        <v>1752</v>
       </c>
       <c r="F89" s="4">
         <v>8.0722891570000002</v>
@@ -5470,7 +5469,7 @@
       </c>
       <c r="M89" s="18">
         <f t="shared" si="3"/>
-        <v>650</v>
+        <v>440</v>
       </c>
       <c r="N89" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5617,7 +5616,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -5666,7 +5665,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>46286.468055555553</v>
       </c>
@@ -6061,7 +6060,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="103" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -6241,7 +6240,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6429,7 +6428,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6688,7 +6687,7 @@
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
     </row>
-    <row r="117" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30">
         <v>46267.425694444442</v>
       </c>
@@ -6738,7 +6737,7 @@
       </c>
       <c r="P117" s="29"/>
     </row>
-    <row r="118" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30">
         <v>46280.593055555553</v>
       </c>
@@ -7012,7 +7011,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="124" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>46243.375</v>
       </c>
@@ -7169,7 +7168,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="5">
-        <v>2348</v>
+        <v>2276</v>
       </c>
       <c r="F127" s="4">
         <v>11.327106349999999</v>
@@ -7194,7 +7193,7 @@
       </c>
       <c r="M127" s="18">
         <f t="shared" si="4"/>
-        <v>1014.5</v>
+        <v>654.5</v>
       </c>
       <c r="N127" s="10" t="str">
         <f t="shared" si="1"/>
@@ -7295,7 +7294,7 @@
       <c r="O129" s="10"/>
       <c r="P129" s="10"/>
     </row>
-    <row r="130" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30">
         <v>46265.375694444447</v>
       </c>
@@ -7344,7 +7343,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="40">
         <v>46243.505555555559</v>
       </c>
@@ -7393,7 +7392,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30">
         <v>46280.588194444441</v>
       </c>
@@ -7443,7 +7442,7 @@
       </c>
       <c r="P132" s="29"/>
     </row>
-    <row r="133" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>46273.375</v>
       </c>
@@ -7831,7 +7830,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46281.375</v>
       </c>
@@ -8010,7 +8009,7 @@
       </c>
       <c r="P145" s="10"/>
     </row>
-    <row r="146" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8130,7 +8129,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="30">
         <v>46281.443055555559</v>
       </c>
@@ -8180,7 +8179,7 @@
       </c>
       <c r="P149" s="29"/>
     </row>
-    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="30">
         <v>46281.388888888891</v>
       </c>
@@ -8686,7 +8685,7 @@
       <c r="O160" s="29"/>
       <c r="P160" s="29"/>
     </row>
-    <row r="161" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -8749,7 +8748,7 @@
         <v>5</v>
       </c>
       <c r="E162" s="4">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="F162" s="4">
         <v>14.17505809</v>
@@ -8774,7 +8773,7 @@
       </c>
       <c r="M162" s="18">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="N162" s="10" t="str">
         <f t="shared" si="5"/>
@@ -9356,7 +9355,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9395,7 +9394,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="6" t="s">
         <v>61</v>
       </c>
@@ -9518,7 +9517,7 @@
       <c r="O180" s="29"/>
       <c r="P180" s="29"/>
     </row>
-    <row r="181" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3">
         <v>46266.375</v>
       </c>
@@ -9775,7 +9774,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -10301,7 +10300,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="6" t="s">
         <v>61</v>
       </c>
@@ -10515,7 +10514,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -11466,7 +11465,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -12251,7 +12250,7 @@
       <c r="O245" s="10"/>
       <c r="P245" s="10"/>
     </row>
-    <row r="246" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -12383,7 +12382,7 @@
       </c>
       <c r="P248" s="29"/>
     </row>
-    <row r="249" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="3">
         <v>46266.375</v>
       </c>
@@ -12432,7 +12431,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="250" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -12699,7 +12698,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -12910,7 +12909,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="261" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -22041,19 +22040,7 @@
       <c r="I981" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P301" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P301">
-      <sortCondition ref="F1:F301"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:P301" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
